--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_broadcasting.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_broadcasting.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08070013145851039</v>
+        <v>0.08060033119559336</v>
       </c>
       <c r="C2">
-        <v>4784.794169860503</v>
+        <v>4749.232928985405</v>
       </c>
       <c r="D2">
-        <v>4310.194169860502</v>
+        <v>4322.554928985404</v>
       </c>
       <c r="E2">
-        <v>-160.2</v>
+        <v>-112.278</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>47.922</v>
       </c>
       <c r="G2">
         <v>474.6</v>
@@ -1439,45 +1439,45 @@
         <v>22.905</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.563827</v>
       </c>
       <c r="N2">
-        <v>22.905</v>
+        <v>20.341173</v>
       </c>
       <c r="O2">
-        <v>4.581</v>
+        <v>4.068234599999999</v>
       </c>
       <c r="P2">
-        <v>18.324</v>
+        <v>16.2729384</v>
       </c>
       <c r="Q2">
-        <v>26.294</v>
+        <v>24.2429384</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08070013145851039</v>
+        <v>0.08098215272282158</v>
       </c>
       <c r="T2">
-        <v>0.6802685217068908</v>
+        <v>0.6857656410742192</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.04024</v>
+        <v>0.0428</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>8.933910127321383</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08060033119559336</v>
+        <v>0.08056933093267635</v>
       </c>
       <c r="C3">
-        <v>4749.232928985405</v>
+        <v>4705.16490994153</v>
       </c>
       <c r="D3">
-        <v>4322.554928985404</v>
+        <v>4326.40890994153</v>
       </c>
       <c r="E3">
-        <v>-112.278</v>
+        <v>-64.35599999999999</v>
       </c>
       <c r="F3">
-        <v>47.922</v>
+        <v>95.84399999999999</v>
       </c>
       <c r="G3">
         <v>474.6</v>
@@ -1521,45 +1521,45 @@
         <v>22.905</v>
       </c>
       <c r="M3">
-        <v>2.563827</v>
+        <v>5.5397832</v>
       </c>
       <c r="N3">
-        <v>20.341173</v>
+        <v>17.3652168</v>
       </c>
       <c r="O3">
-        <v>4.068234599999999</v>
+        <v>3.47304336</v>
       </c>
       <c r="P3">
-        <v>16.2729384</v>
+        <v>13.89217344</v>
       </c>
       <c r="Q3">
-        <v>24.2429384</v>
+        <v>21.86217344</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08098215272282158</v>
+        <v>0.08126992952313913</v>
       </c>
       <c r="T3">
-        <v>0.6857656410742192</v>
+        <v>0.6913749465510849</v>
       </c>
       <c r="U3">
-        <v>0.0535</v>
+        <v>0.0578</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.0428</v>
+        <v>0.04624</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y3">
-        <v>8.933910127321383</v>
+        <v>4.134638337471401</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08056933093267635</v>
+        <v>0.08093593066975932</v>
       </c>
       <c r="C4">
-        <v>4705.16490994153</v>
+        <v>4612.102213831748</v>
       </c>
       <c r="D4">
-        <v>4326.40890994153</v>
+        <v>4281.268213831748</v>
       </c>
       <c r="E4">
-        <v>-64.35599999999999</v>
+        <v>-16.434</v>
       </c>
       <c r="F4">
-        <v>95.84399999999999</v>
+        <v>143.766</v>
       </c>
       <c r="G4">
         <v>474.6</v>
@@ -1603,45 +1603,45 @@
         <v>22.905</v>
       </c>
       <c r="M4">
-        <v>5.5397832</v>
+        <v>10.8974628</v>
       </c>
       <c r="N4">
-        <v>17.3652168</v>
+        <v>12.0075372</v>
       </c>
       <c r="O4">
-        <v>3.47304336</v>
+        <v>2.40150744</v>
       </c>
       <c r="P4">
-        <v>13.89217344</v>
+        <v>9.606029759999998</v>
       </c>
       <c r="Q4">
-        <v>21.86217344</v>
+        <v>17.57602976</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08126992952313913</v>
+        <v>0.08156363986573126</v>
       </c>
       <c r="T4">
-        <v>0.6913749465510849</v>
+        <v>0.6970999078109787</v>
       </c>
       <c r="U4">
-        <v>0.0578</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.04624</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y4">
-        <v>4.134638337471401</v>
+        <v>2.101865399347819</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08093593066975932</v>
+        <v>0.08355694131566781</v>
       </c>
       <c r="C5">
-        <v>4612.102213831748</v>
+        <v>4266.983217056318</v>
       </c>
       <c r="D5">
-        <v>4281.268213831748</v>
+        <v>3984.071217056317</v>
       </c>
       <c r="E5">
-        <v>-16.434</v>
+        <v>31.488</v>
       </c>
       <c r="F5">
-        <v>143.766</v>
+        <v>191.688</v>
       </c>
       <c r="G5">
         <v>474.6</v>
@@ -1685,45 +1685,45 @@
         <v>22.905</v>
       </c>
       <c r="M5">
-        <v>10.8974628</v>
+        <v>28.1397984</v>
       </c>
       <c r="N5">
-        <v>12.0075372</v>
+        <v>-5.234798400000003</v>
       </c>
       <c r="O5">
-        <v>2.40150744</v>
+        <v>-1.046959680000001</v>
       </c>
       <c r="P5">
-        <v>9.606029759999998</v>
+        <v>-4.187838720000002</v>
       </c>
       <c r="Q5">
-        <v>17.57602976</v>
+        <v>3.782161279999998</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08156363986573126</v>
+        <v>0.08191757260342833</v>
       </c>
       <c r="T5">
-        <v>0.6970999078109787</v>
+        <v>0.7039987156433529</v>
       </c>
       <c r="U5">
-        <v>0.07580000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V5">
-        <v>0.2</v>
+        <v>0.1627943432601138</v>
       </c>
       <c r="W5">
-        <v>0.06064000000000001</v>
+        <v>0.1229017904094153</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y5">
-        <v>2.101865399347819</v>
+        <v>0.8139717163005687</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08355694131566781</v>
+        <v>0.0891027186548133</v>
       </c>
       <c r="C6">
-        <v>4266.983217056318</v>
+        <v>3708.821385483137</v>
       </c>
       <c r="D6">
-        <v>3984.071217056317</v>
+        <v>3473.831385483138</v>
       </c>
       <c r="E6">
-        <v>31.488</v>
+        <v>79.41000000000003</v>
       </c>
       <c r="F6">
-        <v>191.688</v>
+        <v>239.61</v>
       </c>
       <c r="G6">
         <v>474.6</v>
@@ -1767,45 +1767,45 @@
         <v>22.905</v>
       </c>
       <c r="M6">
-        <v>28.1397984</v>
+        <v>56.500038</v>
       </c>
       <c r="N6">
-        <v>-5.234798400000003</v>
+        <v>-33.595038</v>
       </c>
       <c r="O6">
-        <v>-1.046959680000001</v>
+        <v>-6.719007600000001</v>
       </c>
       <c r="P6">
-        <v>-4.187838720000002</v>
+        <v>-26.8760304</v>
       </c>
       <c r="Q6">
-        <v>3.782161279999998</v>
+        <v>-18.9060304</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08191757260342833</v>
+        <v>0.08238804951414389</v>
       </c>
       <c r="T6">
-        <v>0.7039987156433529</v>
+        <v>0.7131691863314125</v>
       </c>
       <c r="U6">
-        <v>0.1468</v>
+        <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>0.1627943432601138</v>
+        <v>0.08107959148629244</v>
       </c>
       <c r="W6">
-        <v>0.1229017904094153</v>
+        <v>0.2166814323275323</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y6">
-        <v>0.8139717163005687</v>
+        <v>0.4053979574314622</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0891027186548133</v>
+        <v>0.0910027186548133</v>
       </c>
       <c r="C7">
-        <v>3708.821385483137</v>
+        <v>3514.884282214229</v>
       </c>
       <c r="D7">
-        <v>3473.831385483138</v>
+        <v>3327.816282214229</v>
       </c>
       <c r="E7">
-        <v>79.41000000000003</v>
+        <v>127.3320000000001</v>
       </c>
       <c r="F7">
-        <v>239.61</v>
+        <v>287.532</v>
       </c>
       <c r="G7">
         <v>474.6</v>
@@ -1849,37 +1849,37 @@
         <v>22.905</v>
       </c>
       <c r="M7">
-        <v>56.500038</v>
+        <v>67.80004560000002</v>
       </c>
       <c r="N7">
-        <v>-33.595038</v>
+        <v>-44.89504560000002</v>
       </c>
       <c r="O7">
-        <v>-6.719007600000001</v>
+        <v>-8.979009120000004</v>
       </c>
       <c r="P7">
-        <v>-26.8760304</v>
+        <v>-35.91603648000002</v>
       </c>
       <c r="Q7">
-        <v>-18.9060304</v>
+        <v>-27.94603648000002</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08238804951414389</v>
+        <v>0.08277728408344329</v>
       </c>
       <c r="T7">
-        <v>0.7131691863314125</v>
+        <v>0.7207560925689808</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.08107959148629244</v>
+        <v>0.06756632623857702</v>
       </c>
       <c r="W7">
-        <v>0.2166814323275323</v>
+        <v>0.2198678602729435</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>0.4053979574314622</v>
+        <v>0.3378316311928852</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0910027186548133</v>
+        <v>0.09290271865481332</v>
       </c>
       <c r="C8">
-        <v>3514.884282214229</v>
+        <v>3332.726910737195</v>
       </c>
       <c r="D8">
-        <v>3327.816282214229</v>
+        <v>3193.580910737195</v>
       </c>
       <c r="E8">
-        <v>127.332</v>
+        <v>175.254</v>
       </c>
       <c r="F8">
-        <v>287.532</v>
+        <v>335.454</v>
       </c>
       <c r="G8">
         <v>474.6</v>
@@ -1931,37 +1931,37 @@
         <v>22.905</v>
       </c>
       <c r="M8">
-        <v>67.8000456</v>
+        <v>79.10005319999999</v>
       </c>
       <c r="N8">
-        <v>-44.8950456</v>
+        <v>-56.19505319999999</v>
       </c>
       <c r="O8">
-        <v>-8.979009120000001</v>
+        <v>-11.23901064</v>
       </c>
       <c r="P8">
-        <v>-35.91603648</v>
+        <v>-44.95604255999999</v>
       </c>
       <c r="Q8">
-        <v>-27.94603648</v>
+        <v>-36.98604255999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08277728408344329</v>
+        <v>0.08317488928864161</v>
       </c>
       <c r="T8">
-        <v>0.7207560925689808</v>
+        <v>0.7285061580804751</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.06756632623857704</v>
+        <v>0.05791399391878033</v>
       </c>
       <c r="W8">
-        <v>0.2198678602729435</v>
+        <v>0.2221438802339516</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.3378316311928852</v>
+        <v>0.2895699695939017</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09290271865481331</v>
+        <v>0.09480271865481331</v>
       </c>
       <c r="C9">
-        <v>3332.726910737195</v>
+        <v>3160.979051744684</v>
       </c>
       <c r="D9">
-        <v>3193.580910737196</v>
+        <v>3069.755051744684</v>
       </c>
       <c r="E9">
-        <v>175.254</v>
+        <v>223.176</v>
       </c>
       <c r="F9">
-        <v>335.454</v>
+        <v>383.376</v>
       </c>
       <c r="G9">
         <v>474.6</v>
@@ -2013,37 +2013,37 @@
         <v>22.905</v>
       </c>
       <c r="M9">
-        <v>79.1000532</v>
+        <v>90.40006079999999</v>
       </c>
       <c r="N9">
-        <v>-56.1950532</v>
+        <v>-67.49506079999999</v>
       </c>
       <c r="O9">
-        <v>-11.23901064</v>
+        <v>-13.49901216</v>
       </c>
       <c r="P9">
-        <v>-44.95604256</v>
+        <v>-53.99604863999999</v>
       </c>
       <c r="Q9">
-        <v>-36.98604256</v>
+        <v>-46.02604863999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08317488928864161</v>
+        <v>0.08358113808525727</v>
       </c>
       <c r="T9">
-        <v>0.7285061580804751</v>
+        <v>0.7364247032770019</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.05791399391878032</v>
+        <v>0.05067474467893279</v>
       </c>
       <c r="W9">
-        <v>0.2221438802339516</v>
+        <v>0.2238508952047077</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.2895699695939016</v>
+        <v>0.2533737233946639</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09480271865481331</v>
+        <v>0.09670271865481331</v>
       </c>
       <c r="C10">
-        <v>3160.979051744684</v>
+        <v>2998.475065704467</v>
       </c>
       <c r="D10">
-        <v>3069.755051744684</v>
+        <v>2955.173065704467</v>
       </c>
       <c r="E10">
-        <v>223.176</v>
+        <v>271.098</v>
       </c>
       <c r="F10">
-        <v>383.376</v>
+        <v>431.2979999999999</v>
       </c>
       <c r="G10">
         <v>474.6</v>
@@ -2095,37 +2095,37 @@
         <v>22.905</v>
       </c>
       <c r="M10">
-        <v>90.40006079999999</v>
+        <v>101.7000684</v>
       </c>
       <c r="N10">
-        <v>-67.49506079999999</v>
+        <v>-78.79506839999999</v>
       </c>
       <c r="O10">
-        <v>-13.49901216</v>
+        <v>-15.75901368</v>
       </c>
       <c r="P10">
-        <v>-53.99604863999999</v>
+        <v>-63.03605472</v>
       </c>
       <c r="Q10">
-        <v>-46.02604863999999</v>
+        <v>-55.06605472</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08358113808525727</v>
+        <v>0.08399631542685351</v>
       </c>
       <c r="T10">
-        <v>0.7364247032770019</v>
+        <v>0.7445172824338921</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.05067474467893279</v>
+        <v>0.04504421749238469</v>
       </c>
       <c r="W10">
-        <v>0.2238508952047077</v>
+        <v>0.2251785735152957</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.2533737233946639</v>
+        <v>0.2252210874619235</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09670271865481331</v>
+        <v>0.09860271865481332</v>
       </c>
       <c r="C11">
-        <v>2998.475065704467</v>
+        <v>2844.217085893573</v>
       </c>
       <c r="D11">
-        <v>2955.173065704467</v>
+        <v>2848.837085893573</v>
       </c>
       <c r="E11">
-        <v>271.098</v>
+        <v>319.0199999999999</v>
       </c>
       <c r="F11">
-        <v>431.2979999999999</v>
+        <v>479.2199999999999</v>
       </c>
       <c r="G11">
         <v>474.6</v>
@@ -2177,37 +2177,37 @@
         <v>22.905</v>
       </c>
       <c r="M11">
-        <v>101.7000684</v>
+        <v>113.000076</v>
       </c>
       <c r="N11">
-        <v>-78.79506839999999</v>
+        <v>-90.09507599999998</v>
       </c>
       <c r="O11">
-        <v>-15.75901368</v>
+        <v>-18.01901519999999</v>
       </c>
       <c r="P11">
-        <v>-63.03605472</v>
+        <v>-72.07606079999998</v>
       </c>
       <c r="Q11">
-        <v>-55.06605472</v>
+        <v>-64.10606079999998</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08399631542685351</v>
+        <v>0.08442071893159633</v>
       </c>
       <c r="T11">
-        <v>0.7445172824338921</v>
+        <v>0.7527896966831576</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.04504421749238469</v>
+        <v>0.04053979574314623</v>
       </c>
       <c r="W11">
-        <v>0.2251785735152957</v>
+        <v>0.2262407161637661</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.2252210874619235</v>
+        <v>0.2026989787157312</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09860271865481332</v>
+        <v>0.1005027186548133</v>
       </c>
       <c r="C12">
-        <v>2844.217085893573</v>
+        <v>2697.345881972764</v>
       </c>
       <c r="D12">
-        <v>2848.837085893573</v>
+        <v>2749.887881972764</v>
       </c>
       <c r="E12">
-        <v>319.02</v>
+        <v>366.942</v>
       </c>
       <c r="F12">
-        <v>479.22</v>
+        <v>527.1419999999999</v>
       </c>
       <c r="G12">
         <v>474.6</v>
@@ -2259,37 +2259,37 @@
         <v>22.905</v>
       </c>
       <c r="M12">
-        <v>113.000076</v>
+        <v>124.3000836</v>
       </c>
       <c r="N12">
-        <v>-90.09507600000001</v>
+        <v>-101.3950836</v>
       </c>
       <c r="O12">
-        <v>-18.0190152</v>
+        <v>-20.27901672</v>
       </c>
       <c r="P12">
-        <v>-72.07606080000001</v>
+        <v>-81.11606687999999</v>
       </c>
       <c r="Q12">
-        <v>-64.10606080000001</v>
+        <v>-73.14606687999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08442071893159633</v>
+        <v>0.0848546595937491</v>
       </c>
       <c r="T12">
-        <v>0.7527896966831576</v>
+        <v>0.7612480078818449</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.04053979574314622</v>
+        <v>0.03685435976649657</v>
       </c>
       <c r="W12">
-        <v>0.2262407161637661</v>
+        <v>0.2271097419670601</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.2026989787157312</v>
+        <v>0.1842717988324829</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1005027186548133</v>
+        <v>0.1024027186548133</v>
       </c>
       <c r="C13">
-        <v>2697.345881972764</v>
+        <v>2557.117591746474</v>
       </c>
       <c r="D13">
-        <v>2749.887881972764</v>
+        <v>2657.581591746474</v>
       </c>
       <c r="E13">
-        <v>366.942</v>
+        <v>414.864</v>
       </c>
       <c r="F13">
-        <v>527.1419999999999</v>
+        <v>575.064</v>
       </c>
       <c r="G13">
         <v>474.6</v>
@@ -2341,37 +2341,37 @@
         <v>22.905</v>
       </c>
       <c r="M13">
-        <v>124.3000836</v>
+        <v>135.6000912</v>
       </c>
       <c r="N13">
-        <v>-101.3950836</v>
+        <v>-112.6950912</v>
       </c>
       <c r="O13">
-        <v>-20.27901672</v>
+        <v>-22.53901824</v>
       </c>
       <c r="P13">
-        <v>-81.11606687999999</v>
+        <v>-90.15607296</v>
       </c>
       <c r="Q13">
-        <v>-73.14606687999999</v>
+        <v>-82.18607296</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0848546595937491</v>
+        <v>0.08529846254367807</v>
       </c>
       <c r="T13">
-        <v>0.7612480078818449</v>
+        <v>0.7698985534259566</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.03685435976649657</v>
+        <v>0.03378316311928852</v>
       </c>
       <c r="W13">
-        <v>0.2271097419670601</v>
+        <v>0.2278339301364718</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.1842717988324829</v>
+        <v>0.1689158155964426</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1024027186548133</v>
+        <v>0.1043027186548133</v>
       </c>
       <c r="C14">
-        <v>2557.117591746474</v>
+        <v>2422.88498703575</v>
       </c>
       <c r="D14">
-        <v>2657.581591746474</v>
+        <v>2571.27098703575</v>
       </c>
       <c r="E14">
-        <v>414.864</v>
+        <v>462.786</v>
       </c>
       <c r="F14">
-        <v>575.064</v>
+        <v>622.986</v>
       </c>
       <c r="G14">
         <v>474.6</v>
@@ -2423,37 +2423,37 @@
         <v>22.905</v>
       </c>
       <c r="M14">
-        <v>135.6000912</v>
+        <v>146.9000988</v>
       </c>
       <c r="N14">
-        <v>-112.6950912</v>
+        <v>-123.9950988</v>
       </c>
       <c r="O14">
-        <v>-22.53901824</v>
+        <v>-24.79901976</v>
       </c>
       <c r="P14">
-        <v>-90.15607296</v>
+        <v>-99.19607904</v>
       </c>
       <c r="Q14">
-        <v>-82.18607296</v>
+        <v>-91.22607904</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08529846254367807</v>
+        <v>0.08575246786027206</v>
       </c>
       <c r="T14">
-        <v>0.7698985534259566</v>
+        <v>0.7787479620860251</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.03378316311928852</v>
+        <v>0.03118445826395863</v>
       </c>
       <c r="W14">
-        <v>0.2278339301364718</v>
+        <v>0.2284467047413586</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.1689158155964426</v>
+        <v>0.1559222913197932</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1043027186548133</v>
+        <v>0.1062027186548133</v>
       </c>
       <c r="C15">
-        <v>2422.88498703575</v>
+        <v>2294.082275303437</v>
       </c>
       <c r="D15">
-        <v>2571.27098703575</v>
+        <v>2490.390275303437</v>
       </c>
       <c r="E15">
-        <v>462.786</v>
+        <v>510.708</v>
       </c>
       <c r="F15">
-        <v>622.986</v>
+        <v>670.908</v>
       </c>
       <c r="G15">
         <v>474.6</v>
@@ -2505,37 +2505,37 @@
         <v>22.905</v>
       </c>
       <c r="M15">
-        <v>146.9000988</v>
+        <v>158.2001064</v>
       </c>
       <c r="N15">
-        <v>-123.9950988</v>
+        <v>-135.2951064</v>
       </c>
       <c r="O15">
-        <v>-24.79901976</v>
+        <v>-27.05902128</v>
       </c>
       <c r="P15">
-        <v>-99.19607904</v>
+        <v>-108.23608512</v>
       </c>
       <c r="Q15">
-        <v>-91.22607904</v>
+        <v>-100.26608512</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08575246786027206</v>
+        <v>0.08621703144004267</v>
       </c>
       <c r="T15">
-        <v>0.7787479620860251</v>
+        <v>0.7878031709474905</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.03118445826395863</v>
+        <v>0.02895699695939016</v>
       </c>
       <c r="W15">
-        <v>0.2284467047413586</v>
+        <v>0.2289719401169758</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.1559222913197932</v>
+        <v>0.1447849847969508</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1062027186548133</v>
+        <v>0.1081027186548133</v>
       </c>
       <c r="C16">
-        <v>2294.082275303437</v>
+        <v>2170.212682241044</v>
       </c>
       <c r="D16">
-        <v>2490.390275303437</v>
+        <v>2414.442682241044</v>
       </c>
       <c r="E16">
-        <v>510.708</v>
+        <v>558.6300000000001</v>
       </c>
       <c r="F16">
-        <v>670.908</v>
+        <v>718.83</v>
       </c>
       <c r="G16">
         <v>474.6</v>
@@ -2587,37 +2587,37 @@
         <v>22.905</v>
       </c>
       <c r="M16">
-        <v>158.2001064</v>
+        <v>169.500114</v>
       </c>
       <c r="N16">
-        <v>-135.2951064</v>
+        <v>-146.595114</v>
       </c>
       <c r="O16">
-        <v>-27.05902128</v>
+        <v>-29.31902280000001</v>
       </c>
       <c r="P16">
-        <v>-108.23608512</v>
+        <v>-117.2760912</v>
       </c>
       <c r="Q16">
-        <v>-100.26608512</v>
+        <v>-109.3060912</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08621703144004267</v>
+        <v>0.08669252592757258</v>
       </c>
       <c r="T16">
-        <v>0.7878031709474905</v>
+        <v>0.7970714435468728</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.02895699695939016</v>
+        <v>0.02702653049543081</v>
       </c>
       <c r="W16">
-        <v>0.2289719401169758</v>
+        <v>0.2294271441091774</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.1447849847969508</v>
+        <v>0.1351326524771541</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1081027186548133</v>
+        <v>0.1100027186548133</v>
       </c>
       <c r="C17">
-        <v>2170.212682241045</v>
+        <v>2050.838239223445</v>
       </c>
       <c r="D17">
-        <v>2414.442682241045</v>
+        <v>2342.990239223445</v>
       </c>
       <c r="E17">
-        <v>558.6299999999999</v>
+        <v>606.5519999999999</v>
       </c>
       <c r="F17">
-        <v>718.8299999999999</v>
+        <v>766.752</v>
       </c>
       <c r="G17">
         <v>474.6</v>
@@ -2669,37 +2669,37 @@
         <v>22.905</v>
       </c>
       <c r="M17">
-        <v>169.500114</v>
+        <v>180.8001216</v>
       </c>
       <c r="N17">
-        <v>-146.595114</v>
+        <v>-157.8951216</v>
       </c>
       <c r="O17">
-        <v>-29.3190228</v>
+        <v>-31.57902432</v>
       </c>
       <c r="P17">
-        <v>-117.2760912</v>
+        <v>-126.31609728</v>
       </c>
       <c r="Q17">
-        <v>-109.3060912</v>
+        <v>-118.34609728</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08669252592757258</v>
+        <v>0.08717934171242464</v>
       </c>
       <c r="T17">
-        <v>0.7970714435468728</v>
+        <v>0.8065603893033831</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.02702653049543082</v>
+        <v>0.02533737233946639</v>
       </c>
       <c r="W17">
-        <v>0.2294271441091774</v>
+        <v>0.2298254476023538</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.1351326524771541</v>
+        <v>0.126686861697332</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1100027186548133</v>
+        <v>0.1119027186548133</v>
       </c>
       <c r="C18">
-        <v>2050.838239223445</v>
+        <v>1935.571332007584</v>
       </c>
       <c r="D18">
-        <v>2342.990239223445</v>
+        <v>2275.645332007584</v>
       </c>
       <c r="E18">
-        <v>606.5519999999999</v>
+        <v>654.4739999999999</v>
       </c>
       <c r="F18">
-        <v>766.752</v>
+        <v>814.674</v>
       </c>
       <c r="G18">
         <v>474.6</v>
@@ -2751,37 +2751,37 @@
         <v>22.905</v>
       </c>
       <c r="M18">
-        <v>180.8001216</v>
+        <v>192.1001292</v>
       </c>
       <c r="N18">
-        <v>-157.8951216</v>
+        <v>-169.1951292</v>
       </c>
       <c r="O18">
-        <v>-31.57902432</v>
+        <v>-33.83902584</v>
       </c>
       <c r="P18">
-        <v>-126.31609728</v>
+        <v>-135.35610336</v>
       </c>
       <c r="Q18">
-        <v>-118.34609728</v>
+        <v>-127.38610336</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08717934171242464</v>
+        <v>0.0876778879981165</v>
       </c>
       <c r="T18">
-        <v>0.8065603893033831</v>
+        <v>0.8162779843552312</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.02533737233946639</v>
+        <v>0.02384693867243896</v>
       </c>
       <c r="W18">
-        <v>0.2298254476023538</v>
+        <v>0.2301768918610389</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.126686861697332</v>
+        <v>0.1192346933621948</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1119027186548133</v>
+        <v>0.1138027186548133</v>
       </c>
       <c r="C19">
-        <v>1935.571332007584</v>
+        <v>1824.067666210339</v>
       </c>
       <c r="D19">
-        <v>2275.645332007584</v>
+        <v>2212.063666210339</v>
       </c>
       <c r="E19">
-        <v>654.4739999999999</v>
+        <v>702.3960000000002</v>
       </c>
       <c r="F19">
-        <v>814.674</v>
+        <v>862.5960000000001</v>
       </c>
       <c r="G19">
         <v>474.6</v>
@@ -2833,37 +2833,37 @@
         <v>22.905</v>
       </c>
       <c r="M19">
-        <v>192.1001292</v>
+        <v>203.4001368</v>
       </c>
       <c r="N19">
-        <v>-169.1951292</v>
+        <v>-180.4951368</v>
       </c>
       <c r="O19">
-        <v>-33.83902584</v>
+        <v>-36.09902736000001</v>
       </c>
       <c r="P19">
-        <v>-135.35610336</v>
+        <v>-144.39610944</v>
       </c>
       <c r="Q19">
-        <v>-127.38610336</v>
+        <v>-136.42610944</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0876778879981165</v>
+        <v>0.08818859394931304</v>
       </c>
       <c r="T19">
-        <v>0.8162779843552312</v>
+        <v>0.8262325939205388</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.02384693867243896</v>
+        <v>0.02252210874619234</v>
       </c>
       <c r="W19">
-        <v>0.2301768918610389</v>
+        <v>0.2304892867576478</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.1192346933621948</v>
+        <v>0.1126105437309617</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1138027186548133</v>
+        <v>0.1157027186548133</v>
       </c>
       <c r="C20">
-        <v>1824.067666210339</v>
+        <v>1716.020380002888</v>
       </c>
       <c r="D20">
-        <v>2212.063666210339</v>
+        <v>2151.938380002888</v>
       </c>
       <c r="E20">
-        <v>702.396</v>
+        <v>750.318</v>
       </c>
       <c r="F20">
-        <v>862.5959999999999</v>
+        <v>910.518</v>
       </c>
       <c r="G20">
         <v>474.6</v>
@@ -2915,37 +2915,37 @@
         <v>22.905</v>
       </c>
       <c r="M20">
-        <v>203.4001368</v>
+        <v>214.7001444</v>
       </c>
       <c r="N20">
-        <v>-180.4951368</v>
+        <v>-191.7951444</v>
       </c>
       <c r="O20">
-        <v>-36.09902736</v>
+        <v>-38.35902888</v>
       </c>
       <c r="P20">
-        <v>-144.39610944</v>
+        <v>-153.43611552</v>
       </c>
       <c r="Q20">
-        <v>-136.42610944</v>
+        <v>-145.46611552</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08818859394931304</v>
+        <v>0.08871190992399591</v>
       </c>
       <c r="T20">
-        <v>0.8262325939205388</v>
+        <v>0.8364329963146195</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.02252210874619235</v>
+        <v>0.02133673460165591</v>
       </c>
       <c r="W20">
-        <v>0.2304892867576478</v>
+        <v>0.2307687979809296</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.1126105437309618</v>
+        <v>0.1066836730082795</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1157027186548133</v>
+        <v>0.1176027186548133</v>
       </c>
       <c r="C21">
-        <v>1716.020380002888</v>
+        <v>1611.155091522941</v>
       </c>
       <c r="D21">
-        <v>2151.938380002888</v>
+        <v>2094.995091522941</v>
       </c>
       <c r="E21">
-        <v>750.318</v>
+        <v>798.24</v>
       </c>
       <c r="F21">
-        <v>910.518</v>
+        <v>958.4400000000001</v>
       </c>
       <c r="G21">
         <v>474.6</v>
@@ -2997,37 +2997,37 @@
         <v>22.905</v>
       </c>
       <c r="M21">
-        <v>214.7001444</v>
+        <v>226.000152</v>
       </c>
       <c r="N21">
-        <v>-191.7951444</v>
+        <v>-203.095152</v>
       </c>
       <c r="O21">
-        <v>-38.35902888</v>
+        <v>-40.61903040000001</v>
       </c>
       <c r="P21">
-        <v>-153.43611552</v>
+        <v>-162.4761216</v>
       </c>
       <c r="Q21">
-        <v>-145.46611552</v>
+        <v>-154.5061216</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08871190992399591</v>
+        <v>0.08924830879804585</v>
       </c>
       <c r="T21">
-        <v>0.8364329963146195</v>
+        <v>0.8468884087685522</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.02133673460165591</v>
+        <v>0.02026989787157311</v>
       </c>
       <c r="W21">
-        <v>0.2307687979809296</v>
+        <v>0.2310203580818831</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.1066836730082795</v>
+        <v>0.1013494893578656</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1176027186548133</v>
+        <v>0.1195027186548133</v>
       </c>
       <c r="C22">
-        <v>1611.155091522941</v>
+        <v>1509.225712330645</v>
       </c>
       <c r="D22">
-        <v>2094.995091522941</v>
+        <v>2040.987712330646</v>
       </c>
       <c r="E22">
-        <v>798.24</v>
+        <v>846.162</v>
       </c>
       <c r="F22">
-        <v>958.4400000000001</v>
+        <v>1006.362</v>
       </c>
       <c r="G22">
         <v>474.6</v>
@@ -3079,37 +3079,37 @@
         <v>22.905</v>
       </c>
       <c r="M22">
-        <v>226.000152</v>
+        <v>237.3001596</v>
       </c>
       <c r="N22">
-        <v>-203.095152</v>
+        <v>-214.3951596</v>
       </c>
       <c r="O22">
-        <v>-40.61903040000001</v>
+        <v>-42.87903192000001</v>
       </c>
       <c r="P22">
-        <v>-162.4761216</v>
+        <v>-171.51612768</v>
       </c>
       <c r="Q22">
-        <v>-154.5061216</v>
+        <v>-163.54612768</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08924830879804585</v>
+        <v>0.0897982873904262</v>
       </c>
       <c r="T22">
-        <v>0.8468884087685522</v>
+        <v>0.8576085152086607</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.02026989787157311</v>
+        <v>0.01930466463959344</v>
       </c>
       <c r="W22">
-        <v>0.2310203580818831</v>
+        <v>0.2312479600779839</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.1013494893578656</v>
+        <v>0.09652332319796719</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1195027186548133</v>
+        <v>0.1214027186548133</v>
       </c>
       <c r="C23">
-        <v>1509.225712330645</v>
+        <v>1410.010892146045</v>
       </c>
       <c r="D23">
-        <v>2040.987712330646</v>
+        <v>1989.694892146045</v>
       </c>
       <c r="E23">
-        <v>846.162</v>
+        <v>894.0839999999998</v>
       </c>
       <c r="F23">
-        <v>1006.362</v>
+        <v>1054.284</v>
       </c>
       <c r="G23">
         <v>474.6</v>
@@ -3161,37 +3161,37 @@
         <v>22.905</v>
       </c>
       <c r="M23">
-        <v>237.3001596</v>
+        <v>248.6001672</v>
       </c>
       <c r="N23">
-        <v>-214.3951596</v>
+        <v>-225.6951672</v>
       </c>
       <c r="O23">
-        <v>-42.87903192</v>
+        <v>-45.13903344</v>
       </c>
       <c r="P23">
-        <v>-171.51612768</v>
+        <v>-180.55613376</v>
       </c>
       <c r="Q23">
-        <v>-163.54612768</v>
+        <v>-172.58613376</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0897982873904262</v>
+        <v>0.09036236799799575</v>
       </c>
       <c r="T23">
-        <v>0.8576085152086604</v>
+        <v>0.8686034961728741</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.01930466463959344</v>
+        <v>0.01842717988324829</v>
       </c>
       <c r="W23">
-        <v>0.2312479600779839</v>
+        <v>0.2314548709835301</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.09652332319796719</v>
+        <v>0.09213589941624145</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1214027186548133</v>
+        <v>0.1233027186548133</v>
       </c>
       <c r="C24">
-        <v>1410.010892146045</v>
+        <v>1313.310986535856</v>
       </c>
       <c r="D24">
-        <v>1989.694892146045</v>
+        <v>1940.916986535856</v>
       </c>
       <c r="E24">
-        <v>894.0839999999998</v>
+        <v>942.0059999999999</v>
       </c>
       <c r="F24">
-        <v>1054.284</v>
+        <v>1102.206</v>
       </c>
       <c r="G24">
         <v>474.6</v>
@@ -3243,37 +3243,37 @@
         <v>22.905</v>
       </c>
       <c r="M24">
-        <v>248.6001672</v>
+        <v>259.9001748</v>
       </c>
       <c r="N24">
-        <v>-225.6951672</v>
+        <v>-236.9951748</v>
       </c>
       <c r="O24">
-        <v>-45.13903344</v>
+        <v>-47.39903496</v>
       </c>
       <c r="P24">
-        <v>-180.55613376</v>
+        <v>-189.59613984</v>
       </c>
       <c r="Q24">
-        <v>-172.58613376</v>
+        <v>-181.62613984</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09036236799799575</v>
+        <v>0.09094110004991779</v>
       </c>
       <c r="T24">
-        <v>0.8686034961728741</v>
+        <v>0.8798840610582361</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.01842717988324829</v>
+        <v>0.01762599814919401</v>
       </c>
       <c r="W24">
-        <v>0.2314548709835301</v>
+        <v>0.2316437896364201</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.09213589941624145</v>
+        <v>0.08812999074597005</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1233027186548133</v>
+        <v>0.1252027186548133</v>
       </c>
       <c r="C25">
-        <v>1313.310986535856</v>
+        <v>1218.945459955239</v>
       </c>
       <c r="D25">
-        <v>1940.916986535856</v>
+        <v>1894.473459955239</v>
       </c>
       <c r="E25">
-        <v>942.0059999999999</v>
+        <v>989.9280000000001</v>
       </c>
       <c r="F25">
-        <v>1102.206</v>
+        <v>1150.128</v>
       </c>
       <c r="G25">
         <v>474.6</v>
@@ -3325,37 +3325,37 @@
         <v>22.905</v>
       </c>
       <c r="M25">
-        <v>259.9001748</v>
+        <v>271.2001824000001</v>
       </c>
       <c r="N25">
-        <v>-236.9951748</v>
+        <v>-248.2951824000001</v>
       </c>
       <c r="O25">
-        <v>-47.39903496</v>
+        <v>-49.65903648000002</v>
       </c>
       <c r="P25">
-        <v>-189.59613984</v>
+        <v>-198.63614592</v>
       </c>
       <c r="Q25">
-        <v>-181.62613984</v>
+        <v>-190.66614592</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09094110004991779</v>
+        <v>0.09153506189267986</v>
       </c>
       <c r="T25">
-        <v>0.8798840610582361</v>
+        <v>0.8914614829142656</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.01762599814919401</v>
+        <v>0.01689158155964425</v>
       </c>
       <c r="W25">
-        <v>0.2316437896364201</v>
+        <v>0.2318169650682359</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.08812999074597005</v>
+        <v>0.08445790779822127</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1252027186548133</v>
+        <v>0.1271027186548133</v>
       </c>
       <c r="C26">
-        <v>1218.945459955239</v>
+        <v>1126.750652926518</v>
       </c>
       <c r="D26">
-        <v>1894.473459955239</v>
+        <v>1850.200652926518</v>
       </c>
       <c r="E26">
-        <v>989.9279999999999</v>
+        <v>1037.85</v>
       </c>
       <c r="F26">
-        <v>1150.128</v>
+        <v>1198.05</v>
       </c>
       <c r="G26">
         <v>474.6</v>
@@ -3407,37 +3407,37 @@
         <v>22.905</v>
       </c>
       <c r="M26">
-        <v>271.2001824</v>
+        <v>282.50019</v>
       </c>
       <c r="N26">
-        <v>-248.2951824</v>
+        <v>-259.59519</v>
       </c>
       <c r="O26">
-        <v>-49.65903648</v>
+        <v>-51.919038</v>
       </c>
       <c r="P26">
-        <v>-198.63614592</v>
+        <v>-207.676152</v>
       </c>
       <c r="Q26">
-        <v>-190.66614592</v>
+        <v>-199.706152</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09153506189267986</v>
+        <v>0.09214486271791558</v>
       </c>
       <c r="T26">
-        <v>0.8914614829142656</v>
+        <v>0.9033476360197891</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.01689158155964426</v>
+        <v>0.01621591829725849</v>
       </c>
       <c r="W26">
-        <v>0.2318169650682359</v>
+        <v>0.2319762864655064</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.08445790779822127</v>
+        <v>0.0810795914862924</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1271027186548133</v>
+        <v>0.1290027186548133</v>
       </c>
       <c r="C27">
-        <v>1126.750652926518</v>
+        <v>1036.577855147363</v>
       </c>
       <c r="D27">
-        <v>1850.200652926518</v>
+        <v>1807.949855147363</v>
       </c>
       <c r="E27">
-        <v>1037.85</v>
+        <v>1085.772</v>
       </c>
       <c r="F27">
-        <v>1198.05</v>
+        <v>1245.972</v>
       </c>
       <c r="G27">
         <v>474.6</v>
@@ -3489,37 +3489,37 @@
         <v>22.905</v>
       </c>
       <c r="M27">
-        <v>282.50019</v>
+        <v>293.8001976</v>
       </c>
       <c r="N27">
-        <v>-259.59519</v>
+        <v>-270.8951976</v>
       </c>
       <c r="O27">
-        <v>-51.919038</v>
+        <v>-54.17903952</v>
       </c>
       <c r="P27">
-        <v>-207.676152</v>
+        <v>-216.71615808</v>
       </c>
       <c r="Q27">
-        <v>-199.706152</v>
+        <v>-208.74615808</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09214486271791558</v>
+        <v>0.09277114464653607</v>
       </c>
       <c r="T27">
-        <v>0.9033476360197891</v>
+        <v>0.9155550365065431</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.01621591829725849</v>
+        <v>0.01559222913197932</v>
       </c>
       <c r="W27">
-        <v>0.2319762864655064</v>
+        <v>0.2321233523706793</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.0810795914862924</v>
+        <v>0.07796114565989654</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1290027186548133</v>
+        <v>0.1309027186548133</v>
       </c>
       <c r="C28">
-        <v>1036.577855147363</v>
+        <v>948.2916367172431</v>
       </c>
       <c r="D28">
-        <v>1807.949855147363</v>
+        <v>1767.585636717243</v>
       </c>
       <c r="E28">
-        <v>1085.772</v>
+        <v>1133.694</v>
       </c>
       <c r="F28">
-        <v>1245.972</v>
+        <v>1293.894</v>
       </c>
       <c r="G28">
         <v>474.6</v>
@@ -3571,37 +3571,37 @@
         <v>22.905</v>
       </c>
       <c r="M28">
-        <v>293.8001976</v>
+        <v>305.1002052</v>
       </c>
       <c r="N28">
-        <v>-270.8951976</v>
+        <v>-282.1952052</v>
       </c>
       <c r="O28">
-        <v>-54.17903952</v>
+        <v>-56.43904104000001</v>
       </c>
       <c r="P28">
-        <v>-216.71615808</v>
+        <v>-225.75616416</v>
       </c>
       <c r="Q28">
-        <v>-208.74615808</v>
+        <v>-217.78616416</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09277114464653607</v>
+        <v>0.09341458498415986</v>
       </c>
       <c r="T28">
-        <v>0.9155550365065431</v>
+        <v>0.9280968863217012</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.01559222913197932</v>
+        <v>0.01501473916412823</v>
       </c>
       <c r="W28">
-        <v>0.2321233523706793</v>
+        <v>0.2322595245050986</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.07796114565989654</v>
+        <v>0.07507369582064105</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1309027186548133</v>
+        <v>0.1328027186548133</v>
       </c>
       <c r="C29">
-        <v>948.2916367172431</v>
+        <v>861.7683980239169</v>
       </c>
       <c r="D29">
-        <v>1767.585636717243</v>
+        <v>1728.984398023917</v>
       </c>
       <c r="E29">
-        <v>1133.694</v>
+        <v>1181.616</v>
       </c>
       <c r="F29">
-        <v>1293.894</v>
+        <v>1341.816</v>
       </c>
       <c r="G29">
         <v>474.6</v>
@@ -3653,37 +3653,37 @@
         <v>22.905</v>
       </c>
       <c r="M29">
-        <v>305.1002052</v>
+        <v>316.4002128</v>
       </c>
       <c r="N29">
-        <v>-282.1952052</v>
+        <v>-293.4952128</v>
       </c>
       <c r="O29">
-        <v>-56.43904104000001</v>
+        <v>-58.69904256000001</v>
       </c>
       <c r="P29">
-        <v>-225.75616416</v>
+        <v>-234.79617024</v>
       </c>
       <c r="Q29">
-        <v>-217.78616416</v>
+        <v>-226.82617024</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09341458498415986</v>
+        <v>0.09407589866449541</v>
       </c>
       <c r="T29">
-        <v>0.9280968863217012</v>
+        <v>0.9409871208539471</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.01501473916412823</v>
+        <v>0.01447849847969508</v>
       </c>
       <c r="W29">
-        <v>0.2322595245050986</v>
+        <v>0.2323859700584879</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.07507369582064105</v>
+        <v>0.07239249239847534</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1328027186548133</v>
+        <v>0.1347027186548133</v>
       </c>
       <c r="C30">
-        <v>861.7683980239169</v>
+        <v>776.8951055780633</v>
       </c>
       <c r="D30">
-        <v>1728.984398023917</v>
+        <v>1692.033105578063</v>
       </c>
       <c r="E30">
-        <v>1181.616</v>
+        <v>1229.538</v>
       </c>
       <c r="F30">
-        <v>1341.816</v>
+        <v>1389.738</v>
       </c>
       <c r="G30">
         <v>474.6</v>
@@ -3735,37 +3735,37 @@
         <v>22.905</v>
       </c>
       <c r="M30">
-        <v>316.4002128</v>
+        <v>327.7002204</v>
       </c>
       <c r="N30">
-        <v>-293.4952128</v>
+        <v>-304.7952204000001</v>
       </c>
       <c r="O30">
-        <v>-58.69904256000001</v>
+        <v>-60.95904408000001</v>
       </c>
       <c r="P30">
-        <v>-234.79617024</v>
+        <v>-243.83617632</v>
       </c>
       <c r="Q30">
-        <v>-226.82617024</v>
+        <v>-235.8661763200001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09407589866449541</v>
+        <v>0.09475584089920662</v>
       </c>
       <c r="T30">
-        <v>0.9409871208539471</v>
+        <v>0.9542404605842845</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.01447849847969508</v>
+        <v>0.01397923991142973</v>
       </c>
       <c r="W30">
-        <v>0.2323859700584879</v>
+        <v>0.2325036952288849</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.07239249239847534</v>
+        <v>0.06989619955714854</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1347027186548133</v>
+        <v>0.1366027186548133</v>
       </c>
       <c r="C31">
-        <v>776.8951055780635</v>
+        <v>693.568186559949</v>
       </c>
       <c r="D31">
-        <v>1692.033105578063</v>
+        <v>1656.628186559949</v>
       </c>
       <c r="E31">
-        <v>1229.538</v>
+        <v>1277.46</v>
       </c>
       <c r="F31">
-        <v>1389.738</v>
+        <v>1437.66</v>
       </c>
       <c r="G31">
         <v>474.6</v>
@@ -3817,37 +3817,37 @@
         <v>22.905</v>
       </c>
       <c r="M31">
-        <v>327.7002204</v>
+        <v>339.000228</v>
       </c>
       <c r="N31">
-        <v>-304.7952204</v>
+        <v>-316.095228</v>
       </c>
       <c r="O31">
-        <v>-60.95904408000001</v>
+        <v>-63.21904560000001</v>
       </c>
       <c r="P31">
-        <v>-243.83617632</v>
+        <v>-252.8761824</v>
       </c>
       <c r="Q31">
-        <v>-235.86617632</v>
+        <v>-244.9061824</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09475584089920661</v>
+        <v>0.09545521005490956</v>
       </c>
       <c r="T31">
-        <v>0.9542404605842842</v>
+        <v>0.9678724671640597</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.01397923991142973</v>
+        <v>0.01351326524771541</v>
       </c>
       <c r="W31">
-        <v>0.2325036952288849</v>
+        <v>0.2326135720545887</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.06989619955714854</v>
+        <v>0.06756632623857695</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1366027186548133</v>
+        <v>0.1385027186548133</v>
       </c>
       <c r="C32">
-        <v>693.568186559949</v>
+        <v>611.6925593078263</v>
       </c>
       <c r="D32">
-        <v>1656.628186559949</v>
+        <v>1622.674559307826</v>
       </c>
       <c r="E32">
-        <v>1277.46</v>
+        <v>1325.382</v>
       </c>
       <c r="F32">
-        <v>1437.66</v>
+        <v>1485.582</v>
       </c>
       <c r="G32">
         <v>474.6</v>
@@ -3899,37 +3899,37 @@
         <v>22.905</v>
       </c>
       <c r="M32">
-        <v>339.000228</v>
+        <v>350.3002356</v>
       </c>
       <c r="N32">
-        <v>-316.095228</v>
+        <v>-327.3952356</v>
       </c>
       <c r="O32">
-        <v>-63.21904560000001</v>
+        <v>-65.47904712</v>
       </c>
       <c r="P32">
-        <v>-252.8761824</v>
+        <v>-261.91618848</v>
       </c>
       <c r="Q32">
-        <v>-244.9061824</v>
+        <v>-253.94618848</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09545521005490956</v>
+        <v>0.09617485078034305</v>
       </c>
       <c r="T32">
-        <v>0.9678724671640597</v>
+        <v>0.9818996043693361</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.01351326524771541</v>
+        <v>0.01307735346553104</v>
       </c>
       <c r="W32">
-        <v>0.2326135720545887</v>
+        <v>0.2327163600528278</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.06756632623857695</v>
+        <v>0.06538676732765514</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1385027186548133</v>
+        <v>0.1404027186548133</v>
       </c>
       <c r="C33">
-        <v>611.6925593078263</v>
+        <v>531.1807806363022</v>
       </c>
       <c r="D33">
-        <v>1622.674559307826</v>
+        <v>1590.084780636302</v>
       </c>
       <c r="E33">
-        <v>1325.382</v>
+        <v>1373.304</v>
       </c>
       <c r="F33">
-        <v>1485.582</v>
+        <v>1533.504</v>
       </c>
       <c r="G33">
         <v>474.6</v>
@@ -3981,37 +3981,37 @@
         <v>22.905</v>
       </c>
       <c r="M33">
-        <v>350.3002356</v>
+        <v>361.6002432</v>
       </c>
       <c r="N33">
-        <v>-327.3952356</v>
+        <v>-338.6952432</v>
       </c>
       <c r="O33">
-        <v>-65.47904712</v>
+        <v>-67.73904864000001</v>
       </c>
       <c r="P33">
-        <v>-261.91618848</v>
+        <v>-270.95619456</v>
       </c>
       <c r="Q33">
-        <v>-253.94618848</v>
+        <v>-262.9861945599999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09617485078034305</v>
+        <v>0.09691565740946573</v>
       </c>
       <c r="T33">
-        <v>0.9818996043693361</v>
+        <v>0.996339304433591</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.01307735346553104</v>
+        <v>0.0126686861697332</v>
       </c>
       <c r="W33">
-        <v>0.2327163600528278</v>
+        <v>0.2328127238011769</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.06538676732765514</v>
+        <v>0.06334343084866589</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1404027186548133</v>
+        <v>0.1423027186548133</v>
       </c>
       <c r="C34">
-        <v>531.1807806363022</v>
+        <v>451.952293883161</v>
       </c>
       <c r="D34">
-        <v>1590.084780636302</v>
+        <v>1558.778293883161</v>
       </c>
       <c r="E34">
-        <v>1373.304</v>
+        <v>1421.226</v>
       </c>
       <c r="F34">
-        <v>1533.504</v>
+        <v>1581.426</v>
       </c>
       <c r="G34">
         <v>474.6</v>
@@ -4063,37 +4063,37 @@
         <v>22.905</v>
       </c>
       <c r="M34">
-        <v>361.6002432</v>
+        <v>372.9002508</v>
       </c>
       <c r="N34">
-        <v>-338.6952432</v>
+        <v>-349.9952508</v>
       </c>
       <c r="O34">
-        <v>-67.73904864000001</v>
+        <v>-69.99905016000001</v>
       </c>
       <c r="P34">
-        <v>-270.95619456</v>
+        <v>-279.99620064</v>
       </c>
       <c r="Q34">
-        <v>-262.9861945599999</v>
+        <v>-272.02620064</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09691565740946573</v>
+        <v>0.09767857766930851</v>
       </c>
       <c r="T34">
-        <v>0.996339304433591</v>
+        <v>1.01121004032066</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.0126686861697332</v>
+        <v>0.01228478658883219</v>
       </c>
       <c r="W34">
-        <v>0.2328127238011769</v>
+        <v>0.2329032473223534</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.06334343084866589</v>
+        <v>0.06142393294416093</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1423027186548133</v>
+        <v>0.1442027186548133</v>
       </c>
       <c r="C35">
-        <v>451.952293883161</v>
+        <v>373.9327640703182</v>
       </c>
       <c r="D35">
-        <v>1558.778293883161</v>
+        <v>1528.680764070318</v>
       </c>
       <c r="E35">
-        <v>1421.226</v>
+        <v>1469.148</v>
       </c>
       <c r="F35">
-        <v>1581.426</v>
+        <v>1629.348</v>
       </c>
       <c r="G35">
         <v>474.6</v>
@@ -4145,37 +4145,37 @@
         <v>22.905</v>
       </c>
       <c r="M35">
-        <v>372.9002508</v>
+        <v>384.2002584</v>
       </c>
       <c r="N35">
-        <v>-349.9952508</v>
+        <v>-361.2952584</v>
       </c>
       <c r="O35">
-        <v>-69.99905016000001</v>
+        <v>-72.25905168000001</v>
       </c>
       <c r="P35">
-        <v>-279.99620064</v>
+        <v>-289.03620672</v>
       </c>
       <c r="Q35">
-        <v>-272.02620064</v>
+        <v>-281.06620672</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09767857766930851</v>
+        <v>0.09846461672490409</v>
       </c>
       <c r="T35">
-        <v>1.01121004032066</v>
+        <v>1.026531404567942</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.01228478658883219</v>
+        <v>0.01192346933621948</v>
       </c>
       <c r="W35">
-        <v>0.2329032473223534</v>
+        <v>0.2329884459305195</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.06142393294416093</v>
+        <v>0.05961734668109731</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1442027186548133</v>
+        <v>0.1461027186548133</v>
       </c>
       <c r="C36">
-        <v>373.9327640703182</v>
+        <v>297.0534886276721</v>
       </c>
       <c r="D36">
-        <v>1528.680764070318</v>
+        <v>1499.723488627672</v>
       </c>
       <c r="E36">
-        <v>1469.148</v>
+        <v>1517.07</v>
       </c>
       <c r="F36">
-        <v>1629.348</v>
+        <v>1677.27</v>
       </c>
       <c r="G36">
         <v>474.6</v>
@@ -4227,37 +4227,37 @@
         <v>22.905</v>
       </c>
       <c r="M36">
-        <v>384.2002584</v>
+        <v>395.5002660000001</v>
       </c>
       <c r="N36">
-        <v>-361.2952584</v>
+        <v>-372.5952660000001</v>
       </c>
       <c r="O36">
-        <v>-72.25905168000001</v>
+        <v>-74.51905320000002</v>
       </c>
       <c r="P36">
-        <v>-289.03620672</v>
+        <v>-298.0762128000001</v>
       </c>
       <c r="Q36">
-        <v>-281.06620672</v>
+        <v>-290.1062128</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09846461672490409</v>
+        <v>0.09927484159759492</v>
       </c>
       <c r="T36">
-        <v>1.026531404567942</v>
+        <v>1.042324195407449</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.01192346933621948</v>
+        <v>0.01158279878375606</v>
       </c>
       <c r="W36">
-        <v>0.2329884459305195</v>
+        <v>0.2330687760467904</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.05961734668109731</v>
+        <v>0.05791399391878027</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1461027186548133</v>
+        <v>0.1480027186548133</v>
       </c>
       <c r="C37">
-        <v>297.0534886276721</v>
+        <v>221.2508738466061</v>
       </c>
       <c r="D37">
-        <v>1499.723488627672</v>
+        <v>1471.842873846606</v>
       </c>
       <c r="E37">
-        <v>1517.07</v>
+        <v>1564.992</v>
       </c>
       <c r="F37">
-        <v>1677.27</v>
+        <v>1725.192</v>
       </c>
       <c r="G37">
         <v>474.6</v>
@@ -4309,37 +4309,37 @@
         <v>22.905</v>
       </c>
       <c r="M37">
-        <v>395.5002660000001</v>
+        <v>406.8002736000001</v>
       </c>
       <c r="N37">
-        <v>-372.5952660000001</v>
+        <v>-383.8952736000001</v>
       </c>
       <c r="O37">
-        <v>-74.51905320000002</v>
+        <v>-76.77905472000002</v>
       </c>
       <c r="P37">
-        <v>-298.0762128000001</v>
+        <v>-307.1162188800001</v>
       </c>
       <c r="Q37">
-        <v>-290.1062128</v>
+        <v>-299.14621888</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09927484159759492</v>
+        <v>0.1001103859975573</v>
       </c>
       <c r="T37">
-        <v>1.042324195407449</v>
+        <v>1.05861051096069</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.01158279878375606</v>
+        <v>0.01126105437309617</v>
       </c>
       <c r="W37">
-        <v>0.2330687760467904</v>
+        <v>0.2331446433788239</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.05791399391878027</v>
+        <v>0.05630527186548084</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1480027186548133</v>
+        <v>0.1499027186548133</v>
       </c>
       <c r="C38">
-        <v>221.2508738466065</v>
+        <v>146.4659686656066</v>
       </c>
       <c r="D38">
-        <v>1471.842873846606</v>
+        <v>1444.979968665606</v>
       </c>
       <c r="E38">
-        <v>1564.992</v>
+        <v>1612.914</v>
       </c>
       <c r="F38">
-        <v>1725.192</v>
+        <v>1773.114</v>
       </c>
       <c r="G38">
         <v>474.6</v>
@@ -4391,37 +4391,37 @@
         <v>22.905</v>
       </c>
       <c r="M38">
-        <v>406.8002736</v>
+        <v>418.1002812</v>
       </c>
       <c r="N38">
-        <v>-383.8952736</v>
+        <v>-395.1952812</v>
       </c>
       <c r="O38">
-        <v>-76.77905472</v>
+        <v>-79.03905624000001</v>
       </c>
       <c r="P38">
-        <v>-307.11621888</v>
+        <v>-316.15622496</v>
       </c>
       <c r="Q38">
-        <v>-299.14621888</v>
+        <v>-308.18622496</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1001103859975573</v>
+        <v>0.1009724556165662</v>
       </c>
       <c r="T38">
-        <v>1.05861051096069</v>
+        <v>1.075413852404511</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.01126105437309617</v>
+        <v>0.01095670155220168</v>
       </c>
       <c r="W38">
-        <v>0.2331446433788239</v>
+        <v>0.2332164097739909</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.05630527186548084</v>
+        <v>0.05478350776100838</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1499027186548133</v>
+        <v>0.1518027186548133</v>
       </c>
       <c r="C39">
-        <v>146.4659686656066</v>
+        <v>72.64404859464139</v>
       </c>
       <c r="D39">
-        <v>1444.979968665606</v>
+        <v>1419.080048594642</v>
       </c>
       <c r="E39">
-        <v>1612.914</v>
+        <v>1660.836</v>
       </c>
       <c r="F39">
-        <v>1773.114</v>
+        <v>1821.036</v>
       </c>
       <c r="G39">
         <v>474.6</v>
@@ -4473,37 +4473,37 @@
         <v>22.905</v>
       </c>
       <c r="M39">
-        <v>418.1002812</v>
+        <v>429.4002888000001</v>
       </c>
       <c r="N39">
-        <v>-395.1952812</v>
+        <v>-406.4952888000001</v>
       </c>
       <c r="O39">
-        <v>-79.03905624000001</v>
+        <v>-81.29905776000003</v>
       </c>
       <c r="P39">
-        <v>-316.15622496</v>
+        <v>-325.19623104</v>
       </c>
       <c r="Q39">
-        <v>-308.18622496</v>
+        <v>-317.22623104</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1009724556165662</v>
+        <v>0.1018623339329624</v>
       </c>
       <c r="T39">
-        <v>1.075413852404511</v>
+        <v>1.092759237120713</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.01095670155220168</v>
+        <v>0.01066836730082795</v>
       </c>
       <c r="W39">
-        <v>0.2332164097739909</v>
+        <v>0.2332843989904648</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.05478350776100838</v>
+        <v>0.05334183650413971</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1518027186548133</v>
+        <v>0.1537027186548133</v>
       </c>
       <c r="C40">
-        <v>72.64404859464139</v>
+        <v>-0.2657564017763434</v>
       </c>
       <c r="D40">
-        <v>1419.080048594642</v>
+        <v>1394.092243598224</v>
       </c>
       <c r="E40">
-        <v>1660.836</v>
+        <v>1708.758</v>
       </c>
       <c r="F40">
-        <v>1821.036</v>
+        <v>1868.958</v>
       </c>
       <c r="G40">
         <v>474.6</v>
@@ -4555,37 +4555,37 @@
         <v>22.905</v>
       </c>
       <c r="M40">
-        <v>429.4002888000001</v>
+        <v>440.7002964</v>
       </c>
       <c r="N40">
-        <v>-406.4952888000001</v>
+        <v>-417.7952964</v>
       </c>
       <c r="O40">
-        <v>-81.29905776000003</v>
+        <v>-83.55905928000001</v>
       </c>
       <c r="P40">
-        <v>-325.19623104</v>
+        <v>-334.2362371200001</v>
       </c>
       <c r="Q40">
-        <v>-317.22623104</v>
+        <v>-326.26623712</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1018623339329624</v>
+        <v>0.1027813885876011</v>
       </c>
       <c r="T40">
-        <v>1.092759237120713</v>
+        <v>1.110673322975151</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.01066836730082795</v>
+        <v>0.01039481942131954</v>
       </c>
       <c r="W40">
-        <v>0.2332843989904648</v>
+        <v>0.2333489015804528</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.05334183650413971</v>
+        <v>0.05197409710659762</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1537027186548133</v>
+        <v>0.1556027186548133</v>
       </c>
       <c r="C41">
-        <v>-0.2657564017763434</v>
+        <v>-72.31079538739186</v>
       </c>
       <c r="D41">
-        <v>1394.092243598224</v>
+        <v>1369.969204612608</v>
       </c>
       <c r="E41">
-        <v>1708.758</v>
+        <v>1756.68</v>
       </c>
       <c r="F41">
-        <v>1868.958</v>
+        <v>1916.88</v>
       </c>
       <c r="G41">
         <v>474.6</v>
@@ -4637,37 +4637,37 @@
         <v>22.905</v>
       </c>
       <c r="M41">
-        <v>440.7002964</v>
+        <v>452.000304</v>
       </c>
       <c r="N41">
-        <v>-417.7952964</v>
+        <v>-429.0953040000001</v>
       </c>
       <c r="O41">
-        <v>-83.55905928000001</v>
+        <v>-85.81906080000002</v>
       </c>
       <c r="P41">
-        <v>-334.2362371200001</v>
+        <v>-343.2762432000001</v>
       </c>
       <c r="Q41">
-        <v>-326.26623712</v>
+        <v>-335.3062432</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1027813885876011</v>
+        <v>0.1037310783973945</v>
       </c>
       <c r="T41">
-        <v>1.110673322975151</v>
+        <v>1.129184545024736</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.01039481942131954</v>
+        <v>0.01013494893578656</v>
       </c>
       <c r="W41">
-        <v>0.2333489015804528</v>
+        <v>0.2334101790409415</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.05197409710659762</v>
+        <v>0.05067474467893274</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1556027186548133</v>
+        <v>0.1575027186548133</v>
       </c>
       <c r="C42">
-        <v>-72.31079538739186</v>
+        <v>-143.5351959028858</v>
       </c>
       <c r="D42">
-        <v>1369.969204612608</v>
+        <v>1346.666804097114</v>
       </c>
       <c r="E42">
-        <v>1756.68</v>
+        <v>1804.602</v>
       </c>
       <c r="F42">
-        <v>1916.88</v>
+        <v>1964.802</v>
       </c>
       <c r="G42">
         <v>474.6</v>
@@ -4719,37 +4719,37 @@
         <v>22.905</v>
       </c>
       <c r="M42">
-        <v>452.000304</v>
+        <v>463.3003116</v>
       </c>
       <c r="N42">
-        <v>-429.0953040000001</v>
+        <v>-440.3953116000001</v>
       </c>
       <c r="O42">
-        <v>-85.81906080000002</v>
+        <v>-88.07906232000002</v>
       </c>
       <c r="P42">
-        <v>-343.2762432000001</v>
+        <v>-352.3162492800001</v>
       </c>
       <c r="Q42">
-        <v>-335.3062432</v>
+        <v>-344.3462492800001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1037310783973945</v>
+        <v>0.1047129610820961</v>
       </c>
       <c r="T42">
-        <v>1.129184545024736</v>
+        <v>1.148323266126851</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.01013494893578656</v>
+        <v>0.009887755059303956</v>
       </c>
       <c r="W42">
-        <v>0.2334101790409415</v>
+        <v>0.2334684673570162</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.05067474467893274</v>
+        <v>0.04943877529651974</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1575027186548133</v>
+        <v>0.1594027186548133</v>
       </c>
       <c r="C43">
-        <v>-143.5351959028858</v>
+        <v>-213.9801333649648</v>
       </c>
       <c r="D43">
-        <v>1346.666804097114</v>
+        <v>1324.143866635035</v>
       </c>
       <c r="E43">
-        <v>1804.602</v>
+        <v>1852.524</v>
       </c>
       <c r="F43">
-        <v>1964.802</v>
+        <v>2012.724</v>
       </c>
       <c r="G43">
         <v>474.6</v>
@@ -4801,37 +4801,37 @@
         <v>22.905</v>
       </c>
       <c r="M43">
-        <v>463.3003116</v>
+        <v>474.6003192000001</v>
       </c>
       <c r="N43">
-        <v>-440.3953116000001</v>
+        <v>-451.6953192000001</v>
       </c>
       <c r="O43">
-        <v>-88.07906232000002</v>
+        <v>-90.33906384000002</v>
       </c>
       <c r="P43">
-        <v>-352.3162492800001</v>
+        <v>-361.3562553600001</v>
       </c>
       <c r="Q43">
-        <v>-344.3462492800001</v>
+        <v>-353.3862553600001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1047129610820961</v>
+        <v>0.1057287017904081</v>
       </c>
       <c r="T43">
-        <v>1.148323266126851</v>
+        <v>1.168121943129038</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.009887755059303956</v>
+        <v>0.009652332319796718</v>
       </c>
       <c r="W43">
-        <v>0.2334684673570162</v>
+        <v>0.2335239800389919</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.04943877529651974</v>
+        <v>0.04826166159898349</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1594027186548133</v>
+        <v>0.1613027186548133</v>
       </c>
       <c r="C44">
-        <v>-213.9801333649646</v>
+        <v>-283.6840738760393</v>
       </c>
       <c r="D44">
-        <v>1324.143866635035</v>
+        <v>1302.361926123961</v>
       </c>
       <c r="E44">
-        <v>1852.524</v>
+        <v>1900.446</v>
       </c>
       <c r="F44">
-        <v>2012.724</v>
+        <v>2060.646</v>
       </c>
       <c r="G44">
         <v>474.6</v>
@@ -4883,37 +4883,37 @@
         <v>22.905</v>
       </c>
       <c r="M44">
-        <v>474.6003192</v>
+        <v>485.9003268</v>
       </c>
       <c r="N44">
-        <v>-451.6953192</v>
+        <v>-462.9953268</v>
       </c>
       <c r="O44">
-        <v>-90.33906384000001</v>
+        <v>-92.59906536</v>
       </c>
       <c r="P44">
-        <v>-361.35625536</v>
+        <v>-370.39626144</v>
       </c>
       <c r="Q44">
-        <v>-353.38625536</v>
+        <v>-362.42626144</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1057287017904081</v>
+        <v>0.1067800825235731</v>
       </c>
       <c r="T44">
-        <v>1.168121943129038</v>
+        <v>1.188615310552354</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.00965233231979672</v>
+        <v>0.009427859475150286</v>
       </c>
       <c r="W44">
-        <v>0.2335239800389919</v>
+        <v>0.2335769107357596</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.0482616615989836</v>
+        <v>0.0471392973757514</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1613027186548133</v>
+        <v>0.1632027186548133</v>
       </c>
       <c r="C45">
-        <v>-283.6840738760393</v>
+        <v>-352.6829934566754</v>
       </c>
       <c r="D45">
-        <v>1302.361926123961</v>
+        <v>1281.285006543324</v>
       </c>
       <c r="E45">
-        <v>1900.446</v>
+        <v>1948.368</v>
       </c>
       <c r="F45">
-        <v>2060.646</v>
+        <v>2108.568</v>
       </c>
       <c r="G45">
         <v>474.6</v>
@@ -4965,37 +4965,37 @@
         <v>22.905</v>
       </c>
       <c r="M45">
-        <v>485.9003268</v>
+        <v>497.2003344</v>
       </c>
       <c r="N45">
-        <v>-462.9953268</v>
+        <v>-474.2953344</v>
       </c>
       <c r="O45">
-        <v>-92.59906536</v>
+        <v>-94.85906688</v>
       </c>
       <c r="P45">
-        <v>-370.39626144</v>
+        <v>-379.43626752</v>
       </c>
       <c r="Q45">
-        <v>-362.42626144</v>
+        <v>-371.46626752</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1067800825235731</v>
+        <v>0.107869012568637</v>
       </c>
       <c r="T45">
-        <v>1.188615310552354</v>
+        <v>1.209840583955075</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.009427859475150286</v>
+        <v>0.009213589941624143</v>
       </c>
       <c r="W45">
-        <v>0.2335769107357596</v>
+        <v>0.233627435491765</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.0471392973757514</v>
+        <v>0.04606794970812067</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1632027186548133</v>
+        <v>0.1651027186548133</v>
       </c>
       <c r="C46">
-        <v>-352.6829934566754</v>
+        <v>-421.0105763292336</v>
       </c>
       <c r="D46">
-        <v>1281.285006543324</v>
+        <v>1260.879423670766</v>
       </c>
       <c r="E46">
-        <v>1948.368</v>
+        <v>1996.29</v>
       </c>
       <c r="F46">
-        <v>2108.568</v>
+        <v>2156.49</v>
       </c>
       <c r="G46">
         <v>474.6</v>
@@ -5047,37 +5047,37 @@
         <v>22.905</v>
       </c>
       <c r="M46">
-        <v>497.2003344</v>
+        <v>508.500342</v>
       </c>
       <c r="N46">
-        <v>-474.2953344</v>
+        <v>-485.595342</v>
       </c>
       <c r="O46">
-        <v>-94.85906688</v>
+        <v>-97.1190684</v>
       </c>
       <c r="P46">
-        <v>-379.43626752</v>
+        <v>-388.4762736</v>
       </c>
       <c r="Q46">
-        <v>-371.46626752</v>
+        <v>-380.5062736</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.107869012568637</v>
+        <v>0.1089975400698849</v>
       </c>
       <c r="T46">
-        <v>1.209840583955075</v>
+        <v>1.23183768548153</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.009213589941624143</v>
+        <v>0.009008843498476939</v>
       </c>
       <c r="W46">
-        <v>0.233627435491765</v>
+        <v>0.2336757147030591</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.04606794970812067</v>
+        <v>0.04504421749238463</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1651027186548133</v>
+        <v>0.1670027186548133</v>
       </c>
       <c r="C47">
-        <v>-421.0105763292336</v>
+        <v>-488.6983945514912</v>
       </c>
       <c r="D47">
-        <v>1260.879423670766</v>
+        <v>1241.113605448508</v>
       </c>
       <c r="E47">
-        <v>1996.29</v>
+        <v>2044.212</v>
       </c>
       <c r="F47">
-        <v>2156.49</v>
+        <v>2204.412</v>
       </c>
       <c r="G47">
         <v>474.6</v>
@@ -5129,37 +5129,37 @@
         <v>22.905</v>
       </c>
       <c r="M47">
-        <v>508.500342</v>
+        <v>519.8003496</v>
       </c>
       <c r="N47">
-        <v>-485.595342</v>
+        <v>-496.8953496</v>
       </c>
       <c r="O47">
-        <v>-97.1190684</v>
+        <v>-99.37906992000001</v>
       </c>
       <c r="P47">
-        <v>-388.4762736</v>
+        <v>-397.51627968</v>
       </c>
       <c r="Q47">
-        <v>-380.5062736</v>
+        <v>-389.54627968</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1089975400698849</v>
+        <v>0.1101678648859939</v>
       </c>
       <c r="T47">
-        <v>1.23183768548153</v>
+        <v>1.254649494471929</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.009008843498476939</v>
+        <v>0.008812999074597004</v>
       </c>
       <c r="W47">
-        <v>0.2336757147030591</v>
+        <v>0.23372189481821</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.04504421749238463</v>
+        <v>0.04406499537298503</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1670027186548133</v>
+        <v>0.1689027186548133</v>
       </c>
       <c r="C48">
-        <v>-488.6983945514912</v>
+        <v>-555.7760710151802</v>
       </c>
       <c r="D48">
-        <v>1241.113605448508</v>
+        <v>1221.95792898482</v>
       </c>
       <c r="E48">
-        <v>2044.212</v>
+        <v>2092.134</v>
       </c>
       <c r="F48">
-        <v>2204.412</v>
+        <v>2252.334</v>
       </c>
       <c r="G48">
         <v>474.6</v>
@@ -5211,37 +5211,37 @@
         <v>22.905</v>
       </c>
       <c r="M48">
-        <v>519.8003496</v>
+        <v>531.1003572</v>
       </c>
       <c r="N48">
-        <v>-496.8953496</v>
+        <v>-508.1953572</v>
       </c>
       <c r="O48">
-        <v>-99.37906992000001</v>
+        <v>-101.63907144</v>
       </c>
       <c r="P48">
-        <v>-397.51627968</v>
+        <v>-406.55628576</v>
       </c>
       <c r="Q48">
-        <v>-389.54627968</v>
+        <v>-398.58628576</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1101678648859939</v>
+        <v>0.1113823529027107</v>
       </c>
       <c r="T48">
-        <v>1.254649494471929</v>
+        <v>1.278322126443098</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.008812999074597004</v>
+        <v>0.008625488455988558</v>
       </c>
       <c r="W48">
-        <v>0.23372189481821</v>
+        <v>0.2337661098220779</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.04406499537298503</v>
+        <v>0.0431274422799427</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1689027186548133</v>
+        <v>0.1708027186548133</v>
       </c>
       <c r="C49">
-        <v>-555.7760710151802</v>
+        <v>-622.2714275793883</v>
       </c>
       <c r="D49">
-        <v>1221.95792898482</v>
+        <v>1203.384572420612</v>
       </c>
       <c r="E49">
-        <v>2092.134</v>
+        <v>2140.056</v>
       </c>
       <c r="F49">
-        <v>2252.334</v>
+        <v>2300.256</v>
       </c>
       <c r="G49">
         <v>474.6</v>
@@ -5293,37 +5293,37 @@
         <v>22.905</v>
       </c>
       <c r="M49">
-        <v>531.1003572</v>
+        <v>542.4003648000001</v>
       </c>
       <c r="N49">
-        <v>-508.1953572</v>
+        <v>-519.4953648000002</v>
       </c>
       <c r="O49">
-        <v>-101.63907144</v>
+        <v>-103.89907296</v>
       </c>
       <c r="P49">
-        <v>-406.55628576</v>
+        <v>-415.5962918400002</v>
       </c>
       <c r="Q49">
-        <v>-398.58628576</v>
+        <v>-407.6262918400001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1113823529027107</v>
+        <v>0.1126435519969936</v>
       </c>
       <c r="T49">
-        <v>1.278322126443098</v>
+        <v>1.302905244259311</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.008625488455988558</v>
+        <v>0.008445790779822127</v>
       </c>
       <c r="W49">
-        <v>0.2337661098220779</v>
+        <v>0.233808482534118</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.0431274422799427</v>
+        <v>0.04222895389911063</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1708027186548133</v>
+        <v>0.1727027186548133</v>
       </c>
       <c r="C50">
-        <v>-622.2714275793878</v>
+        <v>-688.2106198967444</v>
       </c>
       <c r="D50">
-        <v>1203.384572420612</v>
+        <v>1185.367380103255</v>
       </c>
       <c r="E50">
-        <v>2140.056</v>
+        <v>2187.978</v>
       </c>
       <c r="F50">
-        <v>2300.256</v>
+        <v>2348.178</v>
       </c>
       <c r="G50">
         <v>474.6</v>
@@ -5375,37 +5375,37 @@
         <v>22.905</v>
       </c>
       <c r="M50">
-        <v>542.4003648</v>
+        <v>553.7003724</v>
       </c>
       <c r="N50">
-        <v>-519.4953648000001</v>
+        <v>-530.7953724</v>
       </c>
       <c r="O50">
-        <v>-103.89907296</v>
+        <v>-106.15907448</v>
       </c>
       <c r="P50">
-        <v>-415.59629184</v>
+        <v>-424.63629792</v>
       </c>
       <c r="Q50">
-        <v>-407.62629184</v>
+        <v>-416.66629792</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1126435519969936</v>
+        <v>0.1139542098792876</v>
       </c>
       <c r="T50">
-        <v>1.302905244259311</v>
+        <v>1.328452405911455</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.00844579077982213</v>
+        <v>0.008273427702682903</v>
       </c>
       <c r="W50">
-        <v>0.233808482534118</v>
+        <v>0.2338491257477074</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.04222895389911063</v>
+        <v>0.04136713851341445</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1727027186548133</v>
+        <v>0.1746027186548133</v>
       </c>
       <c r="C51">
-        <v>-688.2106198967444</v>
+        <v>-753.618260306494</v>
       </c>
       <c r="D51">
-        <v>1185.367380103255</v>
+        <v>1167.881739693506</v>
       </c>
       <c r="E51">
-        <v>2187.978</v>
+        <v>2235.9</v>
       </c>
       <c r="F51">
-        <v>2348.178</v>
+        <v>2396.1</v>
       </c>
       <c r="G51">
         <v>474.6</v>
@@ -5457,37 +5457,37 @@
         <v>22.905</v>
       </c>
       <c r="M51">
-        <v>553.7003724</v>
+        <v>565.00038</v>
       </c>
       <c r="N51">
-        <v>-530.7953724</v>
+        <v>-542.09538</v>
       </c>
       <c r="O51">
-        <v>-106.15907448</v>
+        <v>-108.419076</v>
       </c>
       <c r="P51">
-        <v>-424.63629792</v>
+        <v>-433.676304</v>
       </c>
       <c r="Q51">
-        <v>-416.66629792</v>
+        <v>-425.7063039999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1139542098792876</v>
+        <v>0.1153172940768734</v>
       </c>
       <c r="T51">
-        <v>1.328452405911455</v>
+        <v>1.355021454029684</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.008273427702682903</v>
+        <v>0.008107959148629246</v>
       </c>
       <c r="W51">
-        <v>0.2338491257477074</v>
+        <v>0.2338881432327532</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.04136713851341445</v>
+        <v>0.04053979574314615</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1746027186548133</v>
+        <v>0.1765027186548133</v>
       </c>
       <c r="C52">
-        <v>-753.618260306494</v>
+        <v>-818.5175300087258</v>
       </c>
       <c r="D52">
-        <v>1167.881739693506</v>
+        <v>1150.904469991274</v>
       </c>
       <c r="E52">
-        <v>2235.9</v>
+        <v>2283.822</v>
       </c>
       <c r="F52">
-        <v>2396.1</v>
+        <v>2444.022</v>
       </c>
       <c r="G52">
         <v>474.6</v>
@@ -5539,37 +5539,37 @@
         <v>22.905</v>
       </c>
       <c r="M52">
-        <v>565.00038</v>
+        <v>576.3003876</v>
       </c>
       <c r="N52">
-        <v>-542.09538</v>
+        <v>-553.3953876</v>
       </c>
       <c r="O52">
-        <v>-108.419076</v>
+        <v>-110.67907752</v>
       </c>
       <c r="P52">
-        <v>-433.676304</v>
+        <v>-442.71631008</v>
       </c>
       <c r="Q52">
-        <v>-425.7063039999999</v>
+        <v>-434.74631008</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1153172940768734</v>
+        <v>0.1167360143641565</v>
       </c>
       <c r="T52">
-        <v>1.355021454029684</v>
+        <v>1.382674953091514</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.008107959148629246</v>
+        <v>0.007948979557479651</v>
       </c>
       <c r="W52">
-        <v>0.2338881432327532</v>
+        <v>0.2339256306203463</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.04053979574314615</v>
+        <v>0.0397448977873982</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1765027186548133</v>
+        <v>0.1784027186548133</v>
       </c>
       <c r="C53">
-        <v>-818.5175300087258</v>
+        <v>-882.9302815948663</v>
       </c>
       <c r="D53">
-        <v>1150.904469991274</v>
+        <v>1134.413718405134</v>
       </c>
       <c r="E53">
-        <v>2283.822</v>
+        <v>2331.744</v>
       </c>
       <c r="F53">
-        <v>2444.022</v>
+        <v>2491.944</v>
       </c>
       <c r="G53">
         <v>474.6</v>
@@ -5621,37 +5621,37 @@
         <v>22.905</v>
       </c>
       <c r="M53">
-        <v>576.3003876</v>
+        <v>587.6003952</v>
       </c>
       <c r="N53">
-        <v>-553.3953876</v>
+        <v>-564.6953952</v>
       </c>
       <c r="O53">
-        <v>-110.67907752</v>
+        <v>-112.93907904</v>
       </c>
       <c r="P53">
-        <v>-442.71631008</v>
+        <v>-451.75631616</v>
       </c>
       <c r="Q53">
-        <v>-434.74631008</v>
+        <v>-443.78631616</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1167360143641565</v>
+        <v>0.1182138479967431</v>
       </c>
       <c r="T53">
-        <v>1.382674953091514</v>
+        <v>1.411480681280921</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.007948979557479651</v>
+        <v>0.007796114565989658</v>
       </c>
       <c r="W53">
-        <v>0.2339256306203463</v>
+        <v>0.2339616761853397</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.0397448977873982</v>
+        <v>0.03898057282994827</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1784027186548133</v>
+        <v>0.1803027186548133</v>
       </c>
       <c r="C54">
-        <v>-882.9302815948663</v>
+        <v>-946.8771328880312</v>
       </c>
       <c r="D54">
-        <v>1134.413718405134</v>
+        <v>1118.388867111969</v>
       </c>
       <c r="E54">
-        <v>2331.744</v>
+        <v>2379.666</v>
       </c>
       <c r="F54">
-        <v>2491.944</v>
+        <v>2539.866</v>
       </c>
       <c r="G54">
         <v>474.6</v>
@@ -5703,37 +5703,37 @@
         <v>22.905</v>
       </c>
       <c r="M54">
-        <v>587.6003952</v>
+        <v>598.9004028000001</v>
       </c>
       <c r="N54">
-        <v>-564.6953952</v>
+        <v>-575.9954028000001</v>
       </c>
       <c r="O54">
-        <v>-112.93907904</v>
+        <v>-115.19908056</v>
       </c>
       <c r="P54">
-        <v>-451.75631616</v>
+        <v>-460.7963222400001</v>
       </c>
       <c r="Q54">
-        <v>-443.78631616</v>
+        <v>-452.82632224</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1182138479967431</v>
+        <v>0.1197545681668866</v>
       </c>
       <c r="T54">
-        <v>1.411480681280921</v>
+        <v>1.441512185137962</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.007796114565989658</v>
+        <v>0.00764901806474457</v>
       </c>
       <c r="W54">
-        <v>0.2339616761853397</v>
+        <v>0.2339963615403332</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.03898057282994827</v>
+        <v>0.03824509032372281</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1803027186548133</v>
+        <v>0.1822027186548133</v>
       </c>
       <c r="C55">
-        <v>-946.8771328880312</v>
+        <v>-1010.377552940568</v>
       </c>
       <c r="D55">
-        <v>1118.388867111969</v>
+        <v>1102.810447059432</v>
       </c>
       <c r="E55">
-        <v>2379.666</v>
+        <v>2427.588</v>
       </c>
       <c r="F55">
-        <v>2539.866</v>
+        <v>2587.788</v>
       </c>
       <c r="G55">
         <v>474.6</v>
@@ -5785,37 +5785,37 @@
         <v>22.905</v>
       </c>
       <c r="M55">
-        <v>598.9004028000001</v>
+        <v>610.2004104</v>
       </c>
       <c r="N55">
-        <v>-575.9954028000001</v>
+        <v>-587.2954104</v>
       </c>
       <c r="O55">
-        <v>-115.19908056</v>
+        <v>-117.45908208</v>
       </c>
       <c r="P55">
-        <v>-460.7963222400001</v>
+        <v>-469.83632832</v>
       </c>
       <c r="Q55">
-        <v>-452.82632224</v>
+        <v>-461.86632832</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1197545681668866</v>
+        <v>0.1213622761705145</v>
       </c>
       <c r="T55">
-        <v>1.441512185137962</v>
+        <v>1.472849406554004</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.00764901806474457</v>
+        <v>0.007507369582064116</v>
       </c>
       <c r="W55">
-        <v>0.2339963615403332</v>
+        <v>0.2340297622525493</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.03824509032372281</v>
+        <v>0.03753684791032053</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1822027186548133</v>
+        <v>0.1841027186548133</v>
       </c>
       <c r="C56">
-        <v>-1010.377552940568</v>
+        <v>-1073.44994094301</v>
       </c>
       <c r="D56">
-        <v>1102.810447059432</v>
+        <v>1087.660059056991</v>
       </c>
       <c r="E56">
-        <v>2427.588</v>
+        <v>2475.51</v>
       </c>
       <c r="F56">
-        <v>2587.788</v>
+        <v>2635.71</v>
       </c>
       <c r="G56">
         <v>474.6</v>
@@ -5867,37 +5867,37 @@
         <v>22.905</v>
       </c>
       <c r="M56">
-        <v>610.2004104</v>
+        <v>621.5004180000001</v>
       </c>
       <c r="N56">
-        <v>-587.2954104</v>
+        <v>-598.5954180000001</v>
       </c>
       <c r="O56">
-        <v>-117.45908208</v>
+        <v>-119.7190836</v>
       </c>
       <c r="P56">
-        <v>-469.83632832</v>
+        <v>-478.8763344000001</v>
       </c>
       <c r="Q56">
-        <v>-461.86632832</v>
+        <v>-470.9063344</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1213622761705145</v>
+        <v>0.1230414378631927</v>
       </c>
       <c r="T56">
-        <v>1.472849406554004</v>
+        <v>1.505579393366315</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.007507369582064116</v>
+        <v>0.007370871953299312</v>
       </c>
       <c r="W56">
-        <v>0.2340297622525493</v>
+        <v>0.234061948393412</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.03753684791032053</v>
+        <v>0.03685435976649654</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1841027186548133</v>
+        <v>0.1860027186548133</v>
       </c>
       <c r="C57">
-        <v>-1073.44994094301</v>
+        <v>-1136.111698716868</v>
       </c>
       <c r="D57">
-        <v>1087.660059056991</v>
+        <v>1072.920301283133</v>
       </c>
       <c r="E57">
-        <v>2475.51</v>
+        <v>2523.432</v>
       </c>
       <c r="F57">
-        <v>2635.71</v>
+        <v>2683.632</v>
       </c>
       <c r="G57">
         <v>474.6</v>
@@ -5949,37 +5949,37 @@
         <v>22.905</v>
       </c>
       <c r="M57">
-        <v>621.5004180000001</v>
+        <v>632.8004256</v>
       </c>
       <c r="N57">
-        <v>-598.5954180000001</v>
+        <v>-609.8954256000001</v>
       </c>
       <c r="O57">
-        <v>-119.7190836</v>
+        <v>-121.97908512</v>
       </c>
       <c r="P57">
-        <v>-478.8763344000001</v>
+        <v>-487.91634048</v>
       </c>
       <c r="Q57">
-        <v>-470.9063344</v>
+        <v>-479.94634048</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1230414378631927</v>
+        <v>0.1247969250873561</v>
       </c>
       <c r="T57">
-        <v>1.505579393366315</v>
+        <v>1.539797106851914</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.007370871953299312</v>
+        <v>0.00723924923984754</v>
       </c>
       <c r="W57">
-        <v>0.234061948393412</v>
+        <v>0.234092985029244</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.03685435976649654</v>
+        <v>0.03619624619923767</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1860027186548133</v>
+        <v>0.1879027186548133</v>
       </c>
       <c r="C58">
-        <v>-1136.111698716868</v>
+        <v>-1198.379297391794</v>
       </c>
       <c r="D58">
-        <v>1072.920301283133</v>
+        <v>1058.574702608206</v>
       </c>
       <c r="E58">
-        <v>2523.432</v>
+        <v>2571.354</v>
       </c>
       <c r="F58">
-        <v>2683.632</v>
+        <v>2731.554</v>
       </c>
       <c r="G58">
         <v>474.6</v>
@@ -6031,37 +6031,37 @@
         <v>22.905</v>
       </c>
       <c r="M58">
-        <v>632.8004256</v>
+        <v>644.1004332</v>
       </c>
       <c r="N58">
-        <v>-609.8954256000001</v>
+        <v>-621.1954332</v>
       </c>
       <c r="O58">
-        <v>-121.97908512</v>
+        <v>-124.23908664</v>
       </c>
       <c r="P58">
-        <v>-487.91634048</v>
+        <v>-496.95634656</v>
       </c>
       <c r="Q58">
-        <v>-479.94634048</v>
+        <v>-488.98634656</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1247969250873561</v>
+        <v>0.1266340628800854</v>
       </c>
       <c r="T58">
-        <v>1.539797106851914</v>
+        <v>1.575606341894981</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.00723924923984754</v>
+        <v>0.007112244867218636</v>
       </c>
       <c r="W58">
-        <v>0.234092985029244</v>
+        <v>0.2341229326603099</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.03619624619923767</v>
+        <v>0.0355612243360931</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1879027186548133</v>
+        <v>0.1898027186548133</v>
       </c>
       <c r="C59">
-        <v>-1198.379297391794</v>
+        <v>-1260.268338804233</v>
       </c>
       <c r="D59">
-        <v>1058.574702608206</v>
+        <v>1044.607661195767</v>
       </c>
       <c r="E59">
-        <v>2571.354</v>
+        <v>2619.276</v>
       </c>
       <c r="F59">
-        <v>2731.554</v>
+        <v>2779.476</v>
       </c>
       <c r="G59">
         <v>474.6</v>
@@ -6113,37 +6113,37 @@
         <v>22.905</v>
       </c>
       <c r="M59">
-        <v>644.1004332</v>
+        <v>655.4004408000001</v>
       </c>
       <c r="N59">
-        <v>-621.1954332</v>
+        <v>-632.4954408000001</v>
       </c>
       <c r="O59">
-        <v>-124.23908664</v>
+        <v>-126.49908816</v>
       </c>
       <c r="P59">
-        <v>-496.95634656</v>
+        <v>-505.9963526400001</v>
       </c>
       <c r="Q59">
-        <v>-488.98634656</v>
+        <v>-498.02635264</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1266340628800854</v>
+        <v>0.1285586834248493</v>
       </c>
       <c r="T59">
-        <v>1.575606341894981</v>
+        <v>1.613120778606767</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.007112244867218636</v>
+        <v>0.006989619955714866</v>
       </c>
       <c r="W59">
-        <v>0.2341229326603099</v>
+        <v>0.2341518476144424</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.0355612243360931</v>
+        <v>0.03494809977857427</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1898027186548133</v>
+        <v>0.1917027186548133</v>
       </c>
       <c r="C60">
-        <v>-1260.268338804233</v>
+        <v>-1321.793612098732</v>
       </c>
       <c r="D60">
-        <v>1044.607661195767</v>
+        <v>1031.004387901267</v>
       </c>
       <c r="E60">
-        <v>2619.276</v>
+        <v>2667.198</v>
       </c>
       <c r="F60">
-        <v>2779.476</v>
+        <v>2827.398</v>
       </c>
       <c r="G60">
         <v>474.6</v>
@@ -6195,37 +6195,37 @@
         <v>22.905</v>
       </c>
       <c r="M60">
-        <v>655.4004408</v>
+        <v>666.7004483999999</v>
       </c>
       <c r="N60">
-        <v>-632.4954408</v>
+        <v>-643.7954483999999</v>
       </c>
       <c r="O60">
-        <v>-126.49908816</v>
+        <v>-128.75908968</v>
       </c>
       <c r="P60">
-        <v>-505.99635264</v>
+        <v>-515.03635872</v>
       </c>
       <c r="Q60">
-        <v>-498.02635264</v>
+        <v>-507.0663587199999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1285586834248492</v>
+        <v>0.1305771878986261</v>
       </c>
       <c r="T60">
-        <v>1.613120778606766</v>
+        <v>1.652465187841077</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.006989619955714867</v>
+        <v>0.006871151820872242</v>
       </c>
       <c r="W60">
-        <v>0.2341518476144424</v>
+        <v>0.2341797824006383</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.03494809977857427</v>
+        <v>0.03435575910436117</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1917027186548133</v>
+        <v>0.1936027186548133</v>
       </c>
       <c r="C61">
-        <v>-1321.793612098732</v>
+        <v>-1382.969145963609</v>
       </c>
       <c r="D61">
-        <v>1031.004387901267</v>
+        <v>1017.75085403639</v>
       </c>
       <c r="E61">
-        <v>2667.198</v>
+        <v>2715.12</v>
       </c>
       <c r="F61">
-        <v>2827.398</v>
+        <v>2875.32</v>
       </c>
       <c r="G61">
         <v>474.6</v>
@@ -6277,37 +6277,37 @@
         <v>22.905</v>
       </c>
       <c r="M61">
-        <v>666.7004483999999</v>
+        <v>678.000456</v>
       </c>
       <c r="N61">
-        <v>-643.7954483999999</v>
+        <v>-655.095456</v>
       </c>
       <c r="O61">
-        <v>-128.75908968</v>
+        <v>-131.0190912</v>
       </c>
       <c r="P61">
-        <v>-515.03635872</v>
+        <v>-524.0763648</v>
       </c>
       <c r="Q61">
-        <v>-507.0663587199999</v>
+        <v>-516.1063647999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1305771878986261</v>
+        <v>0.1326966175960917</v>
       </c>
       <c r="T61">
-        <v>1.652465187841077</v>
+        <v>1.693776817537104</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.006871151820872242</v>
+        <v>0.006756632623857704</v>
       </c>
       <c r="W61">
-        <v>0.2341797824006383</v>
+        <v>0.2342067860272944</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.03435575910436117</v>
+        <v>0.03378316311928853</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1936027186548133</v>
+        <v>0.1955027186548133</v>
       </c>
       <c r="C62">
-        <v>-1382.969145963609</v>
+        <v>-1443.808256888816</v>
       </c>
       <c r="D62">
-        <v>1017.75085403639</v>
+        <v>1004.833743111184</v>
       </c>
       <c r="E62">
-        <v>2715.12</v>
+        <v>2763.042</v>
       </c>
       <c r="F62">
-        <v>2875.32</v>
+        <v>2923.242</v>
       </c>
       <c r="G62">
         <v>474.6</v>
@@ -6359,37 +6359,37 @@
         <v>22.905</v>
       </c>
       <c r="M62">
-        <v>678.000456</v>
+        <v>689.3004635999999</v>
       </c>
       <c r="N62">
-        <v>-655.095456</v>
+        <v>-666.3954636</v>
       </c>
       <c r="O62">
-        <v>-131.0190912</v>
+        <v>-133.27909272</v>
       </c>
       <c r="P62">
-        <v>-524.0763648</v>
+        <v>-533.11637088</v>
       </c>
       <c r="Q62">
-        <v>-516.1063647999999</v>
+        <v>-525.1463708799999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1326966175960917</v>
+        <v>0.1349247359959915</v>
       </c>
       <c r="T62">
-        <v>1.693776817537104</v>
+        <v>1.737206992345748</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.006756632623857704</v>
+        <v>0.006645868154614135</v>
       </c>
       <c r="W62">
-        <v>0.2342067860272944</v>
+        <v>0.234232904289142</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.03378316311928853</v>
+        <v>0.0332293407730706</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1955027186548133</v>
+        <v>0.1974027186548133</v>
       </c>
       <c r="C63">
-        <v>-1443.808256888816</v>
+        <v>-1504.323593794985</v>
       </c>
       <c r="D63">
-        <v>1004.833743111184</v>
+        <v>992.2404062050149</v>
       </c>
       <c r="E63">
-        <v>2763.042</v>
+        <v>2810.964</v>
       </c>
       <c r="F63">
-        <v>2923.242</v>
+        <v>2971.164</v>
       </c>
       <c r="G63">
         <v>474.6</v>
@@ -6441,37 +6441,37 @@
         <v>22.905</v>
       </c>
       <c r="M63">
-        <v>689.3004635999999</v>
+        <v>700.6004712</v>
       </c>
       <c r="N63">
-        <v>-666.3954636</v>
+        <v>-677.6954712</v>
       </c>
       <c r="O63">
-        <v>-133.27909272</v>
+        <v>-135.53909424</v>
       </c>
       <c r="P63">
-        <v>-533.11637088</v>
+        <v>-542.15637696</v>
       </c>
       <c r="Q63">
-        <v>-525.1463708799999</v>
+        <v>-534.18637696</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1349247359959915</v>
+        <v>0.1372701237853597</v>
       </c>
       <c r="T63">
-        <v>1.737206992345748</v>
+        <v>1.782922965828531</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.006645868154614135</v>
+        <v>0.006538676732765519</v>
       </c>
       <c r="W63">
-        <v>0.234232904289142</v>
+        <v>0.2342581800264139</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.0332293407730706</v>
+        <v>0.03269338366382757</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1974027186548133</v>
+        <v>0.1993027186548133</v>
       </c>
       <c r="C64">
-        <v>-1504.323593794985</v>
+        <v>-1564.527179348065</v>
       </c>
       <c r="D64">
-        <v>992.2404062050149</v>
+        <v>979.9588206519345</v>
       </c>
       <c r="E64">
-        <v>2810.964</v>
+        <v>2858.886</v>
       </c>
       <c r="F64">
-        <v>2971.164</v>
+        <v>3019.086</v>
       </c>
       <c r="G64">
         <v>474.6</v>
@@ -6523,37 +6523,37 @@
         <v>22.905</v>
       </c>
       <c r="M64">
-        <v>700.6004712</v>
+        <v>711.9004788</v>
       </c>
       <c r="N64">
-        <v>-677.6954712</v>
+        <v>-688.9954788</v>
       </c>
       <c r="O64">
-        <v>-135.53909424</v>
+        <v>-137.79909576</v>
       </c>
       <c r="P64">
-        <v>-542.15637696</v>
+        <v>-551.19638304</v>
       </c>
       <c r="Q64">
-        <v>-534.18637696</v>
+        <v>-543.22638304</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1372701237853597</v>
+        <v>0.1397422892930721</v>
       </c>
       <c r="T64">
-        <v>1.782922965828531</v>
+        <v>1.831110073013086</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.006538676732765519</v>
+        <v>0.006434888213197813</v>
       </c>
       <c r="W64">
-        <v>0.2342581800264139</v>
+        <v>0.234282653359328</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.03269338366382757</v>
+        <v>0.03217444106598899</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1993027186548133</v>
+        <v>0.2012027186548133</v>
       </c>
       <c r="C65">
-        <v>-1564.527179348065</v>
+        <v>-1624.430448243203</v>
       </c>
       <c r="D65">
-        <v>979.9588206519345</v>
+        <v>967.9775517567972</v>
       </c>
       <c r="E65">
-        <v>2858.886</v>
+        <v>2906.808</v>
       </c>
       <c r="F65">
-        <v>3019.086</v>
+        <v>3067.008</v>
       </c>
       <c r="G65">
         <v>474.6</v>
@@ -6605,37 +6605,37 @@
         <v>22.905</v>
       </c>
       <c r="M65">
-        <v>711.9004788</v>
+        <v>723.2004863999999</v>
       </c>
       <c r="N65">
-        <v>-688.9954788</v>
+        <v>-700.2954864</v>
       </c>
       <c r="O65">
-        <v>-137.79909576</v>
+        <v>-140.05909728</v>
       </c>
       <c r="P65">
-        <v>-551.19638304</v>
+        <v>-560.23638912</v>
       </c>
       <c r="Q65">
-        <v>-543.22638304</v>
+        <v>-552.26638912</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1397422892930721</v>
+        <v>0.1423517973289908</v>
       </c>
       <c r="T65">
-        <v>1.831110073013086</v>
+        <v>1.881974241707894</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.006434888213197813</v>
+        <v>0.006334343084866598</v>
       </c>
       <c r="W65">
-        <v>0.234282653359328</v>
+        <v>0.2343063619005885</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.03217444106598899</v>
+        <v>0.031671715424333</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2012027186548133</v>
+        <v>0.2031027186548133</v>
       </c>
       <c r="C66">
-        <v>-1624.430448243203</v>
+        <v>-1684.044282714123</v>
       </c>
       <c r="D66">
-        <v>967.9775517567972</v>
+        <v>956.2857172858764</v>
       </c>
       <c r="E66">
-        <v>2906.808</v>
+        <v>2954.73</v>
       </c>
       <c r="F66">
-        <v>3067.008</v>
+        <v>3114.93</v>
       </c>
       <c r="G66">
         <v>474.6</v>
@@ -6687,37 +6687,37 @@
         <v>22.905</v>
       </c>
       <c r="M66">
-        <v>723.2004863999999</v>
+        <v>734.500494</v>
       </c>
       <c r="N66">
-        <v>-700.2954864</v>
+        <v>-711.595494</v>
       </c>
       <c r="O66">
-        <v>-140.05909728</v>
+        <v>-142.3190988</v>
       </c>
       <c r="P66">
-        <v>-560.23638912</v>
+        <v>-569.2763952</v>
       </c>
       <c r="Q66">
-        <v>-552.26638912</v>
+        <v>-561.3063952</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1423517973289908</v>
+        <v>0.1451104201098191</v>
       </c>
       <c r="T66">
-        <v>1.881974241707894</v>
+        <v>1.93574493432812</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.006334343084866598</v>
+        <v>0.006236891652791727</v>
       </c>
       <c r="W66">
-        <v>0.2343063619005885</v>
+        <v>0.2343293409482717</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.031671715424333</v>
+        <v>0.03118445826395855</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2031027186548133</v>
+        <v>0.2050027186548133</v>
       </c>
       <c r="C67">
-        <v>-1684.044282714123</v>
+        <v>-1743.379045499806</v>
       </c>
       <c r="D67">
-        <v>956.2857172858764</v>
+        <v>944.8729545001939</v>
       </c>
       <c r="E67">
-        <v>2954.73</v>
+        <v>3002.652</v>
       </c>
       <c r="F67">
-        <v>3114.93</v>
+        <v>3162.852</v>
       </c>
       <c r="G67">
         <v>474.6</v>
@@ -6769,37 +6769,37 @@
         <v>22.905</v>
       </c>
       <c r="M67">
-        <v>734.500494</v>
+        <v>745.8005016</v>
       </c>
       <c r="N67">
-        <v>-711.595494</v>
+        <v>-722.8955016</v>
       </c>
       <c r="O67">
-        <v>-142.3190988</v>
+        <v>-144.57910032</v>
       </c>
       <c r="P67">
-        <v>-569.2763952</v>
+        <v>-578.31640128</v>
       </c>
       <c r="Q67">
-        <v>-561.3063952</v>
+        <v>-570.34640128</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1451104201098191</v>
+        <v>0.1480313148189314</v>
       </c>
       <c r="T67">
-        <v>1.93574493432812</v>
+        <v>1.992678608867182</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.006236891652791727</v>
+        <v>0.006142393294416095</v>
       </c>
       <c r="W67">
-        <v>0.2343293409482717</v>
+        <v>0.2343516236611767</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.03118445826395855</v>
+        <v>0.03071196647208041</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2050027186548133</v>
+        <v>0.2069027186548133</v>
       </c>
       <c r="C68">
-        <v>-1743.379045499806</v>
+        <v>-1802.444610478352</v>
       </c>
       <c r="D68">
-        <v>944.8729545001939</v>
+        <v>933.7293895216475</v>
       </c>
       <c r="E68">
-        <v>3002.652</v>
+        <v>3050.574</v>
       </c>
       <c r="F68">
-        <v>3162.852</v>
+        <v>3210.774</v>
       </c>
       <c r="G68">
         <v>474.6</v>
@@ -6851,37 +6851,37 @@
         <v>22.905</v>
       </c>
       <c r="M68">
-        <v>745.8005016</v>
+        <v>757.1005092</v>
       </c>
       <c r="N68">
-        <v>-722.8955016</v>
+        <v>-734.1955092000001</v>
       </c>
       <c r="O68">
-        <v>-144.57910032</v>
+        <v>-146.83910184</v>
       </c>
       <c r="P68">
-        <v>-578.31640128</v>
+        <v>-587.35640736</v>
       </c>
       <c r="Q68">
-        <v>-570.34640128</v>
+        <v>-579.38640736</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1480313148189314</v>
+        <v>0.1511292334498082</v>
       </c>
       <c r="T68">
-        <v>1.992678608867182</v>
+        <v>2.053062809135885</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.006142393294416095</v>
+        <v>0.006050715782559137</v>
       </c>
       <c r="W68">
-        <v>0.2343516236611767</v>
+        <v>0.2343732412184726</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.03071196647208041</v>
+        <v>0.03025357891279568</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2069027186548133</v>
+        <v>0.2088027186548133</v>
       </c>
       <c r="C69">
-        <v>-1802.444610478352</v>
+        <v>-1861.250391158404</v>
       </c>
       <c r="D69">
-        <v>933.7293895216475</v>
+        <v>922.8456088415959</v>
       </c>
       <c r="E69">
-        <v>3050.574</v>
+        <v>3098.496</v>
       </c>
       <c r="F69">
-        <v>3210.774</v>
+        <v>3258.696</v>
       </c>
       <c r="G69">
         <v>474.6</v>
@@ -6933,37 +6933,37 @@
         <v>22.905</v>
       </c>
       <c r="M69">
-        <v>757.1005092</v>
+        <v>768.4005168</v>
       </c>
       <c r="N69">
-        <v>-734.1955092000001</v>
+        <v>-745.4955168</v>
       </c>
       <c r="O69">
-        <v>-146.83910184</v>
+        <v>-149.09910336</v>
       </c>
       <c r="P69">
-        <v>-587.35640736</v>
+        <v>-596.3964134400001</v>
       </c>
       <c r="Q69">
-        <v>-579.38640736</v>
+        <v>-588.42641344</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1511292334498082</v>
+        <v>0.1544207719951147</v>
       </c>
       <c r="T69">
-        <v>2.053062809135885</v>
+        <v>2.117221021921381</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.006050715782559137</v>
+        <v>0.005961734668109739</v>
       </c>
       <c r="W69">
-        <v>0.2343732412184726</v>
+        <v>0.2343942229652597</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.03025357891279568</v>
+        <v>0.02980867334054871</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2088027186548133</v>
+        <v>0.2107027186548133</v>
       </c>
       <c r="C70">
-        <v>-1861.250391158404</v>
+        <v>-1919.8053672009</v>
       </c>
       <c r="D70">
-        <v>922.8456088415959</v>
+        <v>912.2126327991003</v>
       </c>
       <c r="E70">
-        <v>3098.496</v>
+        <v>3146.418</v>
       </c>
       <c r="F70">
-        <v>3258.696</v>
+        <v>3306.618</v>
       </c>
       <c r="G70">
         <v>474.6</v>
@@ -7015,37 +7015,37 @@
         <v>22.905</v>
       </c>
       <c r="M70">
-        <v>768.4005168</v>
+        <v>779.7005244000001</v>
       </c>
       <c r="N70">
-        <v>-745.4955168</v>
+        <v>-756.7955244000001</v>
       </c>
       <c r="O70">
-        <v>-149.09910336</v>
+        <v>-151.35910488</v>
       </c>
       <c r="P70">
-        <v>-596.3964134400001</v>
+        <v>-605.4364195200001</v>
       </c>
       <c r="Q70">
-        <v>-588.42641344</v>
+        <v>-597.46641952</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1544207719951147</v>
+        <v>0.1579246678659248</v>
       </c>
       <c r="T70">
-        <v>2.117221021921381</v>
+        <v>2.185518474241426</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.005961734668109739</v>
+        <v>0.005875332716398003</v>
       </c>
       <c r="W70">
-        <v>0.2343942229652597</v>
+        <v>0.2344145965454734</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.02980867334054871</v>
+        <v>0.02937666358198998</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2107027186548133</v>
+        <v>0.2126027186548133</v>
       </c>
       <c r="C71">
-        <v>-1919.8053672009</v>
+        <v>-1978.118109128225</v>
       </c>
       <c r="D71">
-        <v>912.2126327991003</v>
+        <v>901.8218908717756</v>
       </c>
       <c r="E71">
-        <v>3146.418</v>
+        <v>3194.340000000001</v>
       </c>
       <c r="F71">
-        <v>3306.618</v>
+        <v>3354.54</v>
       </c>
       <c r="G71">
         <v>474.6</v>
@@ -7097,37 +7097,37 @@
         <v>22.905</v>
       </c>
       <c r="M71">
-        <v>779.7005244000001</v>
+        <v>791.0005320000001</v>
       </c>
       <c r="N71">
-        <v>-756.7955244000001</v>
+        <v>-768.0955320000002</v>
       </c>
       <c r="O71">
-        <v>-151.35910488</v>
+        <v>-153.6191064</v>
       </c>
       <c r="P71">
-        <v>-605.4364195200001</v>
+        <v>-614.4764256000001</v>
       </c>
       <c r="Q71">
-        <v>-597.46641952</v>
+        <v>-606.5064256000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1579246678659248</v>
+        <v>0.161662156794789</v>
       </c>
       <c r="T71">
-        <v>2.185518474241426</v>
+        <v>2.258369090049473</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.005875332716398003</v>
+        <v>0.005791399391878031</v>
       </c>
       <c r="W71">
-        <v>0.2344145965454734</v>
+        <v>0.2344343880233952</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.02937666358198998</v>
+        <v>0.02895699695939014</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2126027186548133</v>
+        <v>0.2145027186548133</v>
       </c>
       <c r="C72">
-        <v>-1978.118109128225</v>
+        <v>-2036.19680136365</v>
       </c>
       <c r="D72">
-        <v>901.8218908717756</v>
+        <v>891.6651986363509</v>
       </c>
       <c r="E72">
-        <v>3194.340000000001</v>
+        <v>3242.262000000001</v>
       </c>
       <c r="F72">
-        <v>3354.54</v>
+        <v>3402.462</v>
       </c>
       <c r="G72">
         <v>474.6</v>
@@ -7179,37 +7179,37 @@
         <v>22.905</v>
       </c>
       <c r="M72">
-        <v>791.0005320000001</v>
+        <v>802.3005396000001</v>
       </c>
       <c r="N72">
-        <v>-768.0955320000002</v>
+        <v>-779.3955396000001</v>
       </c>
       <c r="O72">
-        <v>-153.6191064</v>
+        <v>-155.87910792</v>
       </c>
       <c r="P72">
-        <v>-614.4764256000001</v>
+        <v>-623.5164316800001</v>
       </c>
       <c r="Q72">
-        <v>-606.5064256000001</v>
+        <v>-615.5464316800001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.161662156794789</v>
+        <v>0.1656574035808162</v>
       </c>
       <c r="T72">
-        <v>2.258369090049473</v>
+        <v>2.336243886258076</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.005791399391878031</v>
+        <v>0.005709830386358622</v>
       </c>
       <c r="W72">
-        <v>0.2344343880233952</v>
+        <v>0.2344536219948966</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.02895699695939014</v>
+        <v>0.02854915193179308</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2145027186548133</v>
+        <v>0.2164027186548133</v>
       </c>
       <c r="C73">
-        <v>-2036.196801363648</v>
+        <v>-2094.049263731232</v>
       </c>
       <c r="D73">
-        <v>891.6651986363513</v>
+        <v>881.7347362687675</v>
       </c>
       <c r="E73">
-        <v>3242.262</v>
+        <v>3290.184</v>
       </c>
       <c r="F73">
-        <v>3402.462</v>
+        <v>3450.384</v>
       </c>
       <c r="G73">
         <v>474.6</v>
@@ -7261,37 +7261,37 @@
         <v>22.905</v>
       </c>
       <c r="M73">
-        <v>802.3005396</v>
+        <v>813.6005471999999</v>
       </c>
       <c r="N73">
-        <v>-779.3955396</v>
+        <v>-790.6955472</v>
       </c>
       <c r="O73">
-        <v>-155.87910792</v>
+        <v>-158.13910944</v>
       </c>
       <c r="P73">
-        <v>-623.51643168</v>
+        <v>-632.55643776</v>
       </c>
       <c r="Q73">
-        <v>-615.54643168</v>
+        <v>-624.58643776</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1656574035808162</v>
+        <v>0.1699380251372739</v>
       </c>
       <c r="T73">
-        <v>2.336243886258075</v>
+        <v>2.419681167910149</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.005709830386358623</v>
+        <v>0.005630527186548087</v>
       </c>
       <c r="W73">
-        <v>0.2344536219948966</v>
+        <v>0.234472321689412</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.02854915193179308</v>
+        <v>0.02815263593274042</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2164027186548133</v>
+        <v>0.2183027186548133</v>
       </c>
       <c r="C74">
-        <v>-2094.049263731232</v>
+        <v>-2151.682971534881</v>
       </c>
       <c r="D74">
-        <v>881.7347362687675</v>
+        <v>872.0230284651185</v>
       </c>
       <c r="E74">
-        <v>3290.184</v>
+        <v>3338.106</v>
       </c>
       <c r="F74">
-        <v>3450.384</v>
+        <v>3498.306</v>
       </c>
       <c r="G74">
         <v>474.6</v>
@@ -7343,37 +7343,37 @@
         <v>22.905</v>
       </c>
       <c r="M74">
-        <v>813.6005471999999</v>
+        <v>824.9005547999999</v>
       </c>
       <c r="N74">
-        <v>-790.6955472</v>
+        <v>-801.9955547999999</v>
       </c>
       <c r="O74">
-        <v>-158.13910944</v>
+        <v>-160.39911096</v>
       </c>
       <c r="P74">
-        <v>-632.55643776</v>
+        <v>-641.5964438399999</v>
       </c>
       <c r="Q74">
-        <v>-624.58643776</v>
+        <v>-633.6264438399999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1699380251372739</v>
+        <v>0.1745357297719878</v>
       </c>
       <c r="T74">
-        <v>2.419681167910149</v>
+        <v>2.509298988943859</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.005630527186548087</v>
+        <v>0.005553396677143319</v>
       </c>
       <c r="W74">
-        <v>0.234472321689412</v>
+        <v>0.2344905090635296</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.02815263593274042</v>
+        <v>0.02776698338571659</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2183027186548133</v>
+        <v>0.2202027186548133</v>
       </c>
       <c r="C75">
-        <v>-2151.682971534881</v>
+        <v>-2209.105074324924</v>
       </c>
       <c r="D75">
-        <v>872.0230284651185</v>
+        <v>862.5229256750752</v>
       </c>
       <c r="E75">
-        <v>3338.106</v>
+        <v>3386.028</v>
       </c>
       <c r="F75">
-        <v>3498.306</v>
+        <v>3546.228</v>
       </c>
       <c r="G75">
         <v>474.6</v>
@@ -7425,37 +7425,37 @@
         <v>22.905</v>
       </c>
       <c r="M75">
-        <v>824.9005547999999</v>
+        <v>836.2005624</v>
       </c>
       <c r="N75">
-        <v>-801.9955547999999</v>
+        <v>-813.2955624</v>
       </c>
       <c r="O75">
-        <v>-160.39911096</v>
+        <v>-162.65911248</v>
       </c>
       <c r="P75">
-        <v>-641.5964438399999</v>
+        <v>-650.63644992</v>
       </c>
       <c r="Q75">
-        <v>-633.6264438399999</v>
+        <v>-642.66644992</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1745357297719878</v>
+        <v>0.1794871039939873</v>
       </c>
       <c r="T75">
-        <v>2.509298988943859</v>
+        <v>2.605810488518622</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.005553396677143319</v>
+        <v>0.005478350776100841</v>
       </c>
       <c r="W75">
-        <v>0.2344905090635296</v>
+        <v>0.2345082048869954</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.02776698338571659</v>
+        <v>0.02739175388050419</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2202027186548133</v>
+        <v>0.2221027186548133</v>
       </c>
       <c r="C76">
-        <v>-2209.105074324924</v>
+        <v>-2266.32241345121</v>
       </c>
       <c r="D76">
-        <v>862.5229256750752</v>
+        <v>853.2275865487893</v>
       </c>
       <c r="E76">
-        <v>3386.028</v>
+        <v>3433.95</v>
       </c>
       <c r="F76">
-        <v>3546.228</v>
+        <v>3594.15</v>
       </c>
       <c r="G76">
         <v>474.6</v>
@@ -7507,37 +7507,37 @@
         <v>22.905</v>
       </c>
       <c r="M76">
-        <v>836.2005624</v>
+        <v>847.5005699999999</v>
       </c>
       <c r="N76">
-        <v>-813.2955624</v>
+        <v>-824.59557</v>
       </c>
       <c r="O76">
-        <v>-162.65911248</v>
+        <v>-164.919114</v>
       </c>
       <c r="P76">
-        <v>-650.63644992</v>
+        <v>-659.6764559999999</v>
       </c>
       <c r="Q76">
-        <v>-642.66644992</v>
+        <v>-651.7064559999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1794871039939873</v>
+        <v>0.1848345881537468</v>
       </c>
       <c r="T76">
-        <v>2.605810488518622</v>
+        <v>2.710042908059367</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.005478350776100841</v>
+        <v>0.005405306099086164</v>
       </c>
       <c r="W76">
-        <v>0.2345082048869954</v>
+        <v>0.2345254288218355</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.02739175388050419</v>
+        <v>0.0270265304954308</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2221027186548133</v>
+        <v>0.2240027186548133</v>
       </c>
       <c r="C77">
-        <v>-2266.32241345121</v>
+        <v>-2323.341538493298</v>
       </c>
       <c r="D77">
-        <v>853.2275865487893</v>
+        <v>844.1304615067023</v>
       </c>
       <c r="E77">
-        <v>3433.95</v>
+        <v>3481.872</v>
       </c>
       <c r="F77">
-        <v>3594.15</v>
+        <v>3642.072</v>
       </c>
       <c r="G77">
         <v>474.6</v>
@@ -7589,37 +7589,37 @@
         <v>22.905</v>
       </c>
       <c r="M77">
-        <v>847.5005699999999</v>
+        <v>858.8005776000001</v>
       </c>
       <c r="N77">
-        <v>-824.59557</v>
+        <v>-835.8955776000001</v>
       </c>
       <c r="O77">
-        <v>-164.919114</v>
+        <v>-167.17911552</v>
       </c>
       <c r="P77">
-        <v>-659.6764559999999</v>
+        <v>-668.7164620800002</v>
       </c>
       <c r="Q77">
-        <v>-651.7064559999999</v>
+        <v>-660.7464620800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1848345881537468</v>
+        <v>0.1906276959934862</v>
       </c>
       <c r="T77">
-        <v>2.710042908059367</v>
+        <v>2.822961362561841</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.005405306099086164</v>
+        <v>0.005334183650413976</v>
       </c>
       <c r="W77">
-        <v>0.2345254288218355</v>
+        <v>0.2345421994952324</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.0270265304954308</v>
+        <v>0.0266709182520698</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2240027186548133</v>
+        <v>0.2259027186548133</v>
       </c>
       <c r="C78">
-        <v>-2323.341538493298</v>
+        <v>-2380.16872265066</v>
       </c>
       <c r="D78">
-        <v>844.1304615067023</v>
+        <v>835.22527734934</v>
       </c>
       <c r="E78">
-        <v>3481.872</v>
+        <v>3529.794</v>
       </c>
       <c r="F78">
-        <v>3642.072</v>
+        <v>3689.994</v>
       </c>
       <c r="G78">
         <v>474.6</v>
@@ -7671,37 +7671,37 @@
         <v>22.905</v>
       </c>
       <c r="M78">
-        <v>858.8005776000001</v>
+        <v>870.1005852000001</v>
       </c>
       <c r="N78">
-        <v>-835.8955776000001</v>
+        <v>-847.1955852000001</v>
       </c>
       <c r="O78">
-        <v>-167.17911552</v>
+        <v>-169.43911704</v>
       </c>
       <c r="P78">
-        <v>-668.7164620800002</v>
+        <v>-677.7564681600001</v>
       </c>
       <c r="Q78">
-        <v>-660.7464620800001</v>
+        <v>-669.78646816</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1906276959934862</v>
+        <v>0.1969245523410291</v>
       </c>
       <c r="T78">
-        <v>2.822961362561841</v>
+        <v>2.945698813108008</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.005334183650413976</v>
+        <v>0.005264908538070937</v>
       </c>
       <c r="W78">
-        <v>0.2345421994952324</v>
+        <v>0.2345585345667229</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.0266709182520698</v>
+        <v>0.02632454269035467</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2259027186548133</v>
+        <v>0.2278027186548133</v>
       </c>
       <c r="C79">
-        <v>-2380.16872265066</v>
+        <v>-2436.809977168905</v>
       </c>
       <c r="D79">
-        <v>835.22527734934</v>
+        <v>826.5060228310952</v>
       </c>
       <c r="E79">
-        <v>3529.794</v>
+        <v>3577.716</v>
       </c>
       <c r="F79">
-        <v>3689.994</v>
+        <v>3737.916</v>
       </c>
       <c r="G79">
         <v>474.6</v>
@@ -7753,37 +7753,37 @@
         <v>22.905</v>
       </c>
       <c r="M79">
-        <v>870.1005852000001</v>
+        <v>881.4005928</v>
       </c>
       <c r="N79">
-        <v>-847.1955852000001</v>
+        <v>-858.4955928000001</v>
       </c>
       <c r="O79">
-        <v>-169.43911704</v>
+        <v>-171.69911856</v>
       </c>
       <c r="P79">
-        <v>-677.7564681600001</v>
+        <v>-686.7964742400001</v>
       </c>
       <c r="Q79">
-        <v>-669.78646816</v>
+        <v>-678.82647424</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1969245523410291</v>
+        <v>0.2037938501747123</v>
       </c>
       <c r="T79">
-        <v>2.945698813108008</v>
+        <v>3.079594213703827</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.005264908538070937</v>
+        <v>0.005197409710659772</v>
       </c>
       <c r="W79">
-        <v>0.2345585345667229</v>
+        <v>0.2345744507902264</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.02632454269035467</v>
+        <v>0.02598704855329881</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2278027186548133</v>
+        <v>0.2297027186548133</v>
       </c>
       <c r="C80">
-        <v>-2436.809977168905</v>
+        <v>-2493.271064871717</v>
       </c>
       <c r="D80">
-        <v>826.5060228310952</v>
+        <v>817.966935128283</v>
       </c>
       <c r="E80">
-        <v>3577.716</v>
+        <v>3625.638</v>
       </c>
       <c r="F80">
-        <v>3737.916</v>
+        <v>3785.838</v>
       </c>
       <c r="G80">
         <v>474.6</v>
@@ -7835,37 +7835,37 @@
         <v>22.905</v>
       </c>
       <c r="M80">
-        <v>881.4005928</v>
+        <v>892.7006004000001</v>
       </c>
       <c r="N80">
-        <v>-858.4955928000001</v>
+        <v>-869.7956004000001</v>
       </c>
       <c r="O80">
-        <v>-171.69911856</v>
+        <v>-173.95912008</v>
       </c>
       <c r="P80">
-        <v>-686.7964742400001</v>
+        <v>-695.8364803200001</v>
       </c>
       <c r="Q80">
-        <v>-678.82647424</v>
+        <v>-687.8664803200001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2037938501747123</v>
+        <v>0.2113173668496986</v>
       </c>
       <c r="T80">
-        <v>3.079594213703827</v>
+        <v>3.226241557213533</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.005197409710659772</v>
+        <v>0.005131619714322307</v>
       </c>
       <c r="W80">
-        <v>0.2345744507902264</v>
+        <v>0.2345899640713628</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.02598704855329881</v>
+        <v>0.0256580985716115</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2297027186548133</v>
+        <v>0.2316027186548134</v>
       </c>
       <c r="C81">
-        <v>-2493.271064871717</v>
+        <v>-2549.557512862551</v>
       </c>
       <c r="D81">
-        <v>817.966935128283</v>
+        <v>809.6024871374486</v>
       </c>
       <c r="E81">
-        <v>3625.638</v>
+        <v>3673.56</v>
       </c>
       <c r="F81">
-        <v>3785.838</v>
+        <v>3833.76</v>
       </c>
       <c r="G81">
         <v>474.6</v>
@@ -7917,37 +7917,37 @@
         <v>22.905</v>
       </c>
       <c r="M81">
-        <v>892.7006004000001</v>
+        <v>904.0006080000001</v>
       </c>
       <c r="N81">
-        <v>-869.7956004000001</v>
+        <v>-881.0956080000001</v>
       </c>
       <c r="O81">
-        <v>-173.95912008</v>
+        <v>-176.2191216</v>
       </c>
       <c r="P81">
-        <v>-695.8364803200001</v>
+        <v>-704.8764864000001</v>
       </c>
       <c r="Q81">
-        <v>-687.8664803200001</v>
+        <v>-696.9064864000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2113173668496986</v>
+        <v>0.2195932351921835</v>
       </c>
       <c r="T81">
-        <v>3.226241557213533</v>
+        <v>3.38755363507421</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.005131619714322307</v>
+        <v>0.005067474467893278</v>
       </c>
       <c r="W81">
-        <v>0.2345899640713628</v>
+        <v>0.2346050895204708</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.0256580985716115</v>
+        <v>0.02533737233946631</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2316027186548134</v>
+        <v>0.2335027186548133</v>
       </c>
       <c r="C82">
-        <v>-2549.557512862551</v>
+        <v>-2605.674624454888</v>
       </c>
       <c r="D82">
-        <v>809.6024871374486</v>
+        <v>801.4073755451124</v>
       </c>
       <c r="E82">
-        <v>3673.56</v>
+        <v>3721.482</v>
       </c>
       <c r="F82">
-        <v>3833.76</v>
+        <v>3881.682</v>
       </c>
       <c r="G82">
         <v>474.6</v>
@@ -7999,37 +7999,37 @@
         <v>22.905</v>
       </c>
       <c r="M82">
-        <v>904.0006080000001</v>
+        <v>915.3006156000001</v>
       </c>
       <c r="N82">
-        <v>-881.0956080000001</v>
+        <v>-892.3956156000002</v>
       </c>
       <c r="O82">
-        <v>-176.2191216</v>
+        <v>-178.4791231200001</v>
       </c>
       <c r="P82">
-        <v>-704.8764864000001</v>
+        <v>-713.9164924800001</v>
       </c>
       <c r="Q82">
-        <v>-696.9064864000001</v>
+        <v>-705.9464924800001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2195932351921835</v>
+        <v>0.2287402475707195</v>
       </c>
       <c r="T82">
-        <v>3.38755363507421</v>
+        <v>3.565845931657063</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.005067474467893278</v>
+        <v>0.00500491305470941</v>
       </c>
       <c r="W82">
-        <v>0.2346050895204708</v>
+        <v>0.2346198415016995</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.02533737233946631</v>
+        <v>0.02502456527354702</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2335027186548133</v>
+        <v>0.2354027186548133</v>
       </c>
       <c r="C83">
-        <v>-2605.674624454888</v>
+        <v>-2661.62749038518</v>
       </c>
       <c r="D83">
-        <v>801.4073755451124</v>
+        <v>793.3765096148203</v>
       </c>
       <c r="E83">
-        <v>3721.482</v>
+        <v>3769.404</v>
       </c>
       <c r="F83">
-        <v>3881.682</v>
+        <v>3929.604</v>
       </c>
       <c r="G83">
         <v>474.6</v>
@@ -8081,37 +8081,37 @@
         <v>22.905</v>
       </c>
       <c r="M83">
-        <v>915.3006156000001</v>
+        <v>926.6006232000001</v>
       </c>
       <c r="N83">
-        <v>-892.3956156000002</v>
+        <v>-903.6956232000001</v>
       </c>
       <c r="O83">
-        <v>-178.4791231200001</v>
+        <v>-180.73912464</v>
       </c>
       <c r="P83">
-        <v>-713.9164924800001</v>
+        <v>-722.9564985600001</v>
       </c>
       <c r="Q83">
-        <v>-705.9464924800001</v>
+        <v>-714.9864985600001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2287402475707195</v>
+        <v>0.2389035946579817</v>
       </c>
       <c r="T83">
-        <v>3.565845931657063</v>
+        <v>3.763948483415789</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.00500491305470941</v>
+        <v>0.004943877529651978</v>
       </c>
       <c r="W83">
-        <v>0.2346198415016995</v>
+        <v>0.2346342336785081</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.02502456527354702</v>
+        <v>0.02471938764825987</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2354027186548133</v>
+        <v>0.2373027186548133</v>
       </c>
       <c r="C84">
-        <v>-2661.62749038518</v>
+        <v>-2717.420999358299</v>
       </c>
       <c r="D84">
-        <v>793.3765096148203</v>
+        <v>785.5050006417009</v>
       </c>
       <c r="E84">
-        <v>3769.404</v>
+        <v>3817.326</v>
       </c>
       <c r="F84">
-        <v>3929.604</v>
+        <v>3977.526</v>
       </c>
       <c r="G84">
         <v>474.6</v>
@@ -8163,37 +8163,37 @@
         <v>22.905</v>
       </c>
       <c r="M84">
-        <v>926.6006232000001</v>
+        <v>937.9006308000002</v>
       </c>
       <c r="N84">
-        <v>-903.6956232000001</v>
+        <v>-914.9956308000002</v>
       </c>
       <c r="O84">
-        <v>-180.73912464</v>
+        <v>-182.9991261600001</v>
       </c>
       <c r="P84">
-        <v>-722.9564985600001</v>
+        <v>-731.9965046400001</v>
       </c>
       <c r="Q84">
-        <v>-714.9864985600001</v>
+        <v>-724.0265046400001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2389035946579817</v>
+        <v>0.2502626296378629</v>
       </c>
       <c r="T84">
-        <v>3.763948483415789</v>
+        <v>3.985357217734365</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.004943877529651978</v>
+        <v>0.004884312740138098</v>
       </c>
       <c r="W84">
-        <v>0.2346342336785081</v>
+        <v>0.2346482790558754</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.02471938764825987</v>
+        <v>0.02442156370069049</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2373027186548133</v>
+        <v>0.2392027186548134</v>
       </c>
       <c r="C85">
-        <v>-2717.420999358299</v>
+        <v>-2773.05984797139</v>
       </c>
       <c r="D85">
-        <v>785.5050006417009</v>
+        <v>777.7881520286104</v>
       </c>
       <c r="E85">
-        <v>3817.326</v>
+        <v>3865.248000000001</v>
       </c>
       <c r="F85">
-        <v>3977.526</v>
+        <v>4025.448</v>
       </c>
       <c r="G85">
         <v>474.6</v>
@@ -8245,37 +8245,37 @@
         <v>22.905</v>
       </c>
       <c r="M85">
-        <v>937.9006308000002</v>
+        <v>949.2006384000001</v>
       </c>
       <c r="N85">
-        <v>-914.9956308000002</v>
+        <v>-926.2956384000001</v>
       </c>
       <c r="O85">
-        <v>-182.9991261600001</v>
+        <v>-185.25912768</v>
       </c>
       <c r="P85">
-        <v>-731.9965046400001</v>
+        <v>-741.0365107200001</v>
       </c>
       <c r="Q85">
-        <v>-724.0265046400001</v>
+        <v>-733.0665107200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2502626296378629</v>
+        <v>0.2630415439902294</v>
       </c>
       <c r="T85">
-        <v>3.985357217734365</v>
+        <v>4.234442043842764</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.004884312740138098</v>
+        <v>0.004826166159898359</v>
       </c>
       <c r="W85">
-        <v>0.2346482790558754</v>
+        <v>0.234661990019496</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.02442156370069049</v>
+        <v>0.02413083079949174</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2392027186548133</v>
+        <v>0.2411027186548133</v>
       </c>
       <c r="C86">
-        <v>-2773.059847971389</v>
+        <v>-2828.548550058452</v>
       </c>
       <c r="D86">
-        <v>777.788152028611</v>
+        <v>770.2214499415483</v>
       </c>
       <c r="E86">
-        <v>3865.248</v>
+        <v>3913.17</v>
       </c>
       <c r="F86">
-        <v>4025.448</v>
+        <v>4073.37</v>
       </c>
       <c r="G86">
         <v>474.6</v>
@@ -8327,37 +8327,37 @@
         <v>22.905</v>
       </c>
       <c r="M86">
-        <v>949.2006384</v>
+        <v>960.500646</v>
       </c>
       <c r="N86">
-        <v>-926.2956384</v>
+        <v>-937.595646</v>
       </c>
       <c r="O86">
-        <v>-185.25912768</v>
+        <v>-187.5191292</v>
       </c>
       <c r="P86">
-        <v>-741.03651072</v>
+        <v>-750.0765168</v>
       </c>
       <c r="Q86">
-        <v>-733.06651072</v>
+        <v>-742.1065168</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2630415439902293</v>
+        <v>0.2775243135895779</v>
       </c>
       <c r="T86">
-        <v>4.234442043842761</v>
+        <v>4.516738180098945</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.00482616615989836</v>
+        <v>0.004769387734487791</v>
       </c>
       <c r="W86">
-        <v>0.234661990019496</v>
+        <v>0.2346753783722078</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.02413083079949174</v>
+        <v>0.02384693867243892</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2411027186548133</v>
+        <v>0.2430027186548133</v>
       </c>
       <c r="C87">
-        <v>-2828.548550058452</v>
+        <v>-2883.891445494738</v>
       </c>
       <c r="D87">
-        <v>770.2214499415483</v>
+        <v>762.8005545052608</v>
       </c>
       <c r="E87">
-        <v>3913.17</v>
+        <v>3961.092</v>
       </c>
       <c r="F87">
-        <v>4073.37</v>
+        <v>4121.291999999999</v>
       </c>
       <c r="G87">
         <v>474.6</v>
@@ -8409,37 +8409,37 @@
         <v>22.905</v>
       </c>
       <c r="M87">
-        <v>960.500646</v>
+        <v>971.8006535999999</v>
       </c>
       <c r="N87">
-        <v>-937.595646</v>
+        <v>-948.8956535999999</v>
       </c>
       <c r="O87">
-        <v>-187.5191292</v>
+        <v>-189.77913072</v>
       </c>
       <c r="P87">
-        <v>-750.0765168</v>
+        <v>-759.1165228799999</v>
       </c>
       <c r="Q87">
-        <v>-742.1065168</v>
+        <v>-751.1465228799999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2775243135895779</v>
+        <v>0.2940760502745478</v>
       </c>
       <c r="T87">
-        <v>4.516738180098945</v>
+        <v>4.839362335820299</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.004769387734487791</v>
+        <v>0.004713929737575143</v>
       </c>
       <c r="W87">
-        <v>0.2346753783722078</v>
+        <v>0.2346884553678798</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.02384693867243892</v>
+        <v>0.0235696486878757</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2430027186548133</v>
+        <v>0.2449027186548133</v>
       </c>
       <c r="C88">
-        <v>-2883.891445494738</v>
+        <v>-2939.092708497032</v>
       </c>
       <c r="D88">
-        <v>762.8005545052608</v>
+        <v>755.5212915029676</v>
       </c>
       <c r="E88">
-        <v>3961.092</v>
+        <v>4009.014</v>
       </c>
       <c r="F88">
-        <v>4121.291999999999</v>
+        <v>4169.214</v>
       </c>
       <c r="G88">
         <v>474.6</v>
@@ -8491,37 +8491,37 @@
         <v>22.905</v>
       </c>
       <c r="M88">
-        <v>971.8006535999999</v>
+        <v>983.1006612</v>
       </c>
       <c r="N88">
-        <v>-948.8956535999999</v>
+        <v>-960.1956612</v>
       </c>
       <c r="O88">
-        <v>-189.77913072</v>
+        <v>-192.03913224</v>
       </c>
       <c r="P88">
-        <v>-759.1165228799999</v>
+        <v>-768.1565289600001</v>
       </c>
       <c r="Q88">
-        <v>-751.1465228799999</v>
+        <v>-760.18652896</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2940760502745478</v>
+        <v>0.3131742079879746</v>
       </c>
       <c r="T88">
-        <v>4.839362335820299</v>
+        <v>5.211620977037245</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.004713929737575143</v>
+        <v>0.004659746637143244</v>
       </c>
       <c r="W88">
-        <v>0.2346884553678798</v>
+        <v>0.2347012317429616</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.0235696486878757</v>
+        <v>0.02329873318571618</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2449027186548133</v>
+        <v>0.2468027186548133</v>
       </c>
       <c r="C89">
-        <v>-2939.092708497032</v>
+        <v>-2994.156355453165</v>
       </c>
       <c r="D89">
-        <v>755.5212915029676</v>
+        <v>748.3796445468346</v>
       </c>
       <c r="E89">
-        <v>4009.014</v>
+        <v>4056.936</v>
       </c>
       <c r="F89">
-        <v>4169.214</v>
+        <v>4217.136</v>
       </c>
       <c r="G89">
         <v>474.6</v>
@@ -8573,37 +8573,37 @@
         <v>22.905</v>
       </c>
       <c r="M89">
-        <v>983.1006612</v>
+        <v>994.4006687999999</v>
       </c>
       <c r="N89">
-        <v>-960.1956612</v>
+        <v>-971.4956688</v>
       </c>
       <c r="O89">
-        <v>-192.03913224</v>
+        <v>-194.29913376</v>
       </c>
       <c r="P89">
-        <v>-768.1565289600001</v>
+        <v>-777.19653504</v>
       </c>
       <c r="Q89">
-        <v>-760.18652896</v>
+        <v>-769.2265350399999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3131742079879746</v>
+        <v>0.3354553919869724</v>
       </c>
       <c r="T89">
-        <v>5.211620977037245</v>
+        <v>5.645922725123683</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.004659746637143244</v>
+        <v>0.004606794970812071</v>
       </c>
       <c r="W89">
-        <v>0.2347012317429616</v>
+        <v>0.2347137177458825</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.02329873318571618</v>
+        <v>0.02303397485406034</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2468027186548133</v>
+        <v>0.2487027186548133</v>
       </c>
       <c r="C90">
-        <v>-2994.156355453165</v>
+        <v>-3049.08625231165</v>
       </c>
       <c r="D90">
-        <v>748.3796445468346</v>
+        <v>741.3717476883501</v>
       </c>
       <c r="E90">
-        <v>4056.936</v>
+        <v>4104.858</v>
       </c>
       <c r="F90">
-        <v>4217.136</v>
+        <v>4265.058</v>
       </c>
       <c r="G90">
         <v>474.6</v>
@@ -8655,37 +8655,37 @@
         <v>22.905</v>
       </c>
       <c r="M90">
-        <v>994.4006687999999</v>
+        <v>1005.7006764</v>
       </c>
       <c r="N90">
-        <v>-971.4956688</v>
+        <v>-982.7956764</v>
       </c>
       <c r="O90">
-        <v>-194.29913376</v>
+        <v>-196.55913528</v>
       </c>
       <c r="P90">
-        <v>-777.19653504</v>
+        <v>-786.2365411200001</v>
       </c>
       <c r="Q90">
-        <v>-769.2265350399999</v>
+        <v>-778.2665411200001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3354553919869724</v>
+        <v>0.3617877003494245</v>
       </c>
       <c r="T90">
-        <v>5.645922725123683</v>
+        <v>6.159188427407654</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.004606794970812071</v>
+        <v>0.004555033229566991</v>
       </c>
       <c r="W90">
-        <v>0.2347137177458825</v>
+        <v>0.2347259231644681</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.02303397485406034</v>
+        <v>0.02277516614783492</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2487027186548133</v>
+        <v>0.2506027186548133</v>
       </c>
       <c r="C91">
-        <v>-3049.08625231165</v>
+        <v>-3103.886121559967</v>
       </c>
       <c r="D91">
-        <v>741.3717476883501</v>
+        <v>734.4938784400323</v>
       </c>
       <c r="E91">
-        <v>4104.858</v>
+        <v>4152.78</v>
       </c>
       <c r="F91">
-        <v>4265.058</v>
+        <v>4312.98</v>
       </c>
       <c r="G91">
         <v>474.6</v>
@@ -8737,37 +8737,37 @@
         <v>22.905</v>
       </c>
       <c r="M91">
-        <v>1005.7006764</v>
+        <v>1017.000684</v>
       </c>
       <c r="N91">
-        <v>-982.7956764</v>
+        <v>-994.095684</v>
       </c>
       <c r="O91">
-        <v>-196.55913528</v>
+        <v>-198.8191368</v>
       </c>
       <c r="P91">
-        <v>-786.2365411200001</v>
+        <v>-795.2765472</v>
       </c>
       <c r="Q91">
-        <v>-778.2665411200001</v>
+        <v>-787.3065472</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3617877003494245</v>
+        <v>0.393386470384367</v>
       </c>
       <c r="T91">
-        <v>6.159188427407654</v>
+        <v>6.775107270148419</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.004555033229566991</v>
+        <v>0.00450442174923847</v>
       </c>
       <c r="W91">
-        <v>0.2347259231644681</v>
+        <v>0.2347378573515296</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.02277516614783492</v>
+        <v>0.02252210874619232</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2506027186548133</v>
+        <v>0.2525027186548133</v>
       </c>
       <c r="C92">
-        <v>-3103.886121559967</v>
+        <v>-3158.559548818003</v>
       </c>
       <c r="D92">
-        <v>734.4938784400323</v>
+        <v>727.7424511819969</v>
       </c>
       <c r="E92">
-        <v>4152.78</v>
+        <v>4200.702</v>
       </c>
       <c r="F92">
-        <v>4312.98</v>
+        <v>4360.902</v>
       </c>
       <c r="G92">
         <v>474.6</v>
@@ -8819,37 +8819,37 @@
         <v>22.905</v>
       </c>
       <c r="M92">
-        <v>1017.000684</v>
+        <v>1028.3006916</v>
       </c>
       <c r="N92">
-        <v>-994.095684</v>
+        <v>-1005.3956916</v>
       </c>
       <c r="O92">
-        <v>-198.8191368</v>
+        <v>-201.0791383200001</v>
       </c>
       <c r="P92">
-        <v>-795.2765472</v>
+        <v>-804.3165532800001</v>
       </c>
       <c r="Q92">
-        <v>-787.3065472</v>
+        <v>-796.3465532800001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.393386470384367</v>
+        <v>0.4320071893159634</v>
       </c>
       <c r="T92">
-        <v>6.775107270148419</v>
+        <v>7.527896966831578</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.00450442174923847</v>
+        <v>0.004454922609136947</v>
       </c>
       <c r="W92">
-        <v>0.2347378573515296</v>
+        <v>0.2347495292487655</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.02252210874619232</v>
+        <v>0.02227461304568468</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2525027186548133</v>
+        <v>0.2544027186548133</v>
       </c>
       <c r="C93">
-        <v>-3158.559548818003</v>
+        <v>-3213.109989071142</v>
       </c>
       <c r="D93">
-        <v>727.7424511819969</v>
+        <v>721.1140109288579</v>
       </c>
       <c r="E93">
-        <v>4200.702</v>
+        <v>4248.624</v>
       </c>
       <c r="F93">
-        <v>4360.902</v>
+        <v>4408.824</v>
       </c>
       <c r="G93">
         <v>474.6</v>
@@ -8901,37 +8901,37 @@
         <v>22.905</v>
       </c>
       <c r="M93">
-        <v>1028.3006916</v>
+        <v>1039.6006992</v>
       </c>
       <c r="N93">
-        <v>-1005.3956916</v>
+        <v>-1016.6956992</v>
       </c>
       <c r="O93">
-        <v>-201.0791383200001</v>
+        <v>-203.33913984</v>
       </c>
       <c r="P93">
-        <v>-804.3165532800001</v>
+        <v>-813.35655936</v>
       </c>
       <c r="Q93">
-        <v>-796.3465532800001</v>
+        <v>-805.38655936</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4320071893159634</v>
+        <v>0.4802830879804589</v>
       </c>
       <c r="T93">
-        <v>7.527896966831578</v>
+        <v>8.468884087685527</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.004454922609136947</v>
+        <v>0.004406499537298502</v>
       </c>
       <c r="W93">
-        <v>0.2347495292487655</v>
+        <v>0.234760947409105</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.02227461304568468</v>
+        <v>0.02203249768649251</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2544027186548133</v>
+        <v>0.2563027186548133</v>
       </c>
       <c r="C94">
-        <v>-3213.109989071142</v>
+        <v>-3267.540772565817</v>
       </c>
       <c r="D94">
-        <v>721.1140109288579</v>
+        <v>714.6052274341826</v>
       </c>
       <c r="E94">
-        <v>4248.624</v>
+        <v>4296.546</v>
       </c>
       <c r="F94">
-        <v>4408.824</v>
+        <v>4456.746</v>
       </c>
       <c r="G94">
         <v>474.6</v>
@@ -8983,37 +8983,37 @@
         <v>22.905</v>
       </c>
       <c r="M94">
-        <v>1039.6006992</v>
+        <v>1050.9007068</v>
       </c>
       <c r="N94">
-        <v>-1016.6956992</v>
+        <v>-1027.9957068</v>
       </c>
       <c r="O94">
-        <v>-203.33913984</v>
+        <v>-205.59914136</v>
       </c>
       <c r="P94">
-        <v>-813.35655936</v>
+        <v>-822.3965654400001</v>
       </c>
       <c r="Q94">
-        <v>-805.38655936</v>
+        <v>-814.4265654400001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4802830879804589</v>
+        <v>0.5423521005490959</v>
       </c>
       <c r="T94">
-        <v>8.468884087685527</v>
+        <v>9.678724671640603</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.004406499537298502</v>
+        <v>0.004359117821843679</v>
       </c>
       <c r="W94">
-        <v>0.234760947409105</v>
+        <v>0.2347721200176092</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.02203249768649251</v>
+        <v>0.02179558910921842</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2563027186548133</v>
+        <v>0.2582027186548133</v>
       </c>
       <c r="C95">
-        <v>-3267.540772565817</v>
+        <v>-3321.855110388628</v>
       </c>
       <c r="D95">
-        <v>714.6052274341826</v>
+        <v>708.212889611372</v>
       </c>
       <c r="E95">
-        <v>4296.546</v>
+        <v>4344.468</v>
       </c>
       <c r="F95">
-        <v>4456.746</v>
+        <v>4504.668</v>
       </c>
       <c r="G95">
         <v>474.6</v>
@@ -9065,37 +9065,37 @@
         <v>22.905</v>
       </c>
       <c r="M95">
-        <v>1050.9007068</v>
+        <v>1062.2007144</v>
       </c>
       <c r="N95">
-        <v>-1027.9957068</v>
+        <v>-1039.2957144</v>
       </c>
       <c r="O95">
-        <v>-205.59914136</v>
+        <v>-207.85914288</v>
       </c>
       <c r="P95">
-        <v>-822.3965654400001</v>
+        <v>-831.4365715199999</v>
       </c>
       <c r="Q95">
-        <v>-814.4265654400001</v>
+        <v>-823.4665715199999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5423521005490959</v>
+        <v>0.6251107839739453</v>
       </c>
       <c r="T95">
-        <v>9.678724671640603</v>
+        <v>11.29184545024737</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.004359117821843679</v>
+        <v>0.004312744227994279</v>
       </c>
       <c r="W95">
-        <v>0.2347721200176092</v>
+        <v>0.234783054911039</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.02179558910921842</v>
+        <v>0.0215637211399714</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2582027186548133</v>
+        <v>0.2601027186548133</v>
       </c>
       <c r="C96">
-        <v>-3321.855110388628</v>
+        <v>-3376.05609974867</v>
       </c>
       <c r="D96">
-        <v>708.212889611372</v>
+        <v>701.9339002513302</v>
       </c>
       <c r="E96">
-        <v>4344.468</v>
+        <v>4392.39</v>
       </c>
       <c r="F96">
-        <v>4504.668</v>
+        <v>4552.59</v>
       </c>
       <c r="G96">
         <v>474.6</v>
@@ -9147,37 +9147,37 @@
         <v>22.905</v>
       </c>
       <c r="M96">
-        <v>1062.2007144</v>
+        <v>1073.500722</v>
       </c>
       <c r="N96">
-        <v>-1039.2957144</v>
+        <v>-1050.595722</v>
       </c>
       <c r="O96">
-        <v>-207.85914288</v>
+        <v>-210.1191444</v>
       </c>
       <c r="P96">
-        <v>-831.4365715199999</v>
+        <v>-840.4765776</v>
       </c>
       <c r="Q96">
-        <v>-823.4665715199999</v>
+        <v>-832.5065776</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6251107839739453</v>
+        <v>0.7409729407687347</v>
       </c>
       <c r="T96">
-        <v>11.29184545024737</v>
+        <v>13.55021454029685</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.004312744227994279</v>
+        <v>0.004267346920331181</v>
       </c>
       <c r="W96">
-        <v>0.234783054911039</v>
+        <v>0.2347937595961859</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.0215637211399714</v>
+        <v>0.02133673460165586</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2601027186548133</v>
+        <v>0.2620027186548133</v>
       </c>
       <c r="C97">
-        <v>-3376.05609974867</v>
+        <v>-3430.146728981344</v>
       </c>
       <c r="D97">
-        <v>701.9339002513302</v>
+        <v>695.7652710186566</v>
       </c>
       <c r="E97">
-        <v>4392.39</v>
+        <v>4440.312000000001</v>
       </c>
       <c r="F97">
-        <v>4552.59</v>
+        <v>4600.512000000001</v>
       </c>
       <c r="G97">
         <v>474.6</v>
@@ -9229,37 +9229,37 @@
         <v>22.905</v>
       </c>
       <c r="M97">
-        <v>1073.500722</v>
+        <v>1084.8007296</v>
       </c>
       <c r="N97">
-        <v>-1050.595722</v>
+        <v>-1061.8957296</v>
       </c>
       <c r="O97">
-        <v>-210.1191444</v>
+        <v>-212.3791459200001</v>
       </c>
       <c r="P97">
-        <v>-840.4765776</v>
+        <v>-849.5165836800003</v>
       </c>
       <c r="Q97">
-        <v>-832.5065776</v>
+        <v>-841.5465836800003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7409729407687347</v>
+        <v>0.9147661759609188</v>
       </c>
       <c r="T97">
-        <v>13.55021454029685</v>
+        <v>16.93776817537108</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.004267346920331181</v>
+        <v>0.004222895389911063</v>
       </c>
       <c r="W97">
-        <v>0.2347937595961859</v>
+        <v>0.234804241267059</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.02133673460165586</v>
+        <v>0.02111447694955526</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2620027186548133</v>
+        <v>0.2639027186548133</v>
       </c>
       <c r="C98">
-        <v>-3430.146728981343</v>
+        <v>-3484.129882290613</v>
       </c>
       <c r="D98">
-        <v>695.7652710186566</v>
+        <v>689.7041177093867</v>
       </c>
       <c r="E98">
-        <v>4440.312</v>
+        <v>4488.233999999999</v>
       </c>
       <c r="F98">
-        <v>4600.512</v>
+        <v>4648.433999999999</v>
       </c>
       <c r="G98">
         <v>474.6</v>
@@ -9311,37 +9311,37 @@
         <v>22.905</v>
       </c>
       <c r="M98">
-        <v>1084.8007296</v>
+        <v>1096.1007372</v>
       </c>
       <c r="N98">
-        <v>-1061.8957296</v>
+        <v>-1073.1957372</v>
       </c>
       <c r="O98">
-        <v>-212.37914592</v>
+        <v>-214.63914744</v>
       </c>
       <c r="P98">
-        <v>-849.5165836800001</v>
+        <v>-858.55658976</v>
       </c>
       <c r="Q98">
-        <v>-841.54658368</v>
+        <v>-850.5865897599999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9147661759609166</v>
+        <v>1.204421567947889</v>
       </c>
       <c r="T98">
-        <v>16.93776817537103</v>
+        <v>22.58369090049471</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.004222895389911065</v>
+        <v>0.004179360385891363</v>
       </c>
       <c r="W98">
-        <v>0.234804241267059</v>
+        <v>0.2348145068210068</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.02111447694955526</v>
+        <v>0.02089680192945675</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2639027186548133</v>
+        <v>0.2658027186548133</v>
       </c>
       <c r="C99">
-        <v>-3484.129882290613</v>
+        <v>-3538.00834424554</v>
       </c>
       <c r="D99">
-        <v>689.7041177093867</v>
+        <v>683.7476557544596</v>
       </c>
       <c r="E99">
-        <v>4488.233999999999</v>
+        <v>4536.156</v>
       </c>
       <c r="F99">
-        <v>4648.433999999999</v>
+        <v>4696.356</v>
       </c>
       <c r="G99">
         <v>474.6</v>
@@ -9393,37 +9393,37 @@
         <v>22.905</v>
       </c>
       <c r="M99">
-        <v>1096.1007372</v>
+        <v>1107.4007448</v>
       </c>
       <c r="N99">
-        <v>-1073.1957372</v>
+        <v>-1084.4957448</v>
       </c>
       <c r="O99">
-        <v>-214.63914744</v>
+        <v>-216.89914896</v>
       </c>
       <c r="P99">
-        <v>-858.55658976</v>
+        <v>-867.59659584</v>
       </c>
       <c r="Q99">
-        <v>-850.5865897599999</v>
+        <v>-859.6265958399999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.204421567947889</v>
+        <v>1.783732351921833</v>
       </c>
       <c r="T99">
-        <v>22.58369090049471</v>
+        <v>33.87553635074207</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.004179360385891363</v>
+        <v>0.004136713851341452</v>
       </c>
       <c r="W99">
-        <v>0.2348145068210068</v>
+        <v>0.2348245628738537</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.02089680192945675</v>
+        <v>0.02068356925670722</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2658027186548133</v>
+        <v>0.2677027186548133</v>
       </c>
       <c r="C100">
-        <v>-3538.00834424554</v>
+        <v>-3591.784804045802</v>
       </c>
       <c r="D100">
-        <v>683.7476557544596</v>
+        <v>677.8931959541978</v>
       </c>
       <c r="E100">
-        <v>4536.156</v>
+        <v>4584.078</v>
       </c>
       <c r="F100">
-        <v>4696.356</v>
+        <v>4744.277999999999</v>
       </c>
       <c r="G100">
         <v>474.6</v>
@@ -9475,37 +9475,37 @@
         <v>22.905</v>
       </c>
       <c r="M100">
-        <v>1107.4007448</v>
+        <v>1118.7007524</v>
       </c>
       <c r="N100">
-        <v>-1084.4957448</v>
+        <v>-1095.7957524</v>
       </c>
       <c r="O100">
-        <v>-216.89914896</v>
+        <v>-219.15915048</v>
       </c>
       <c r="P100">
-        <v>-867.59659584</v>
+        <v>-876.6366019199999</v>
       </c>
       <c r="Q100">
-        <v>-859.6265958399999</v>
+        <v>-868.6666019199998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.783732351921833</v>
+        <v>3.521664703843666</v>
       </c>
       <c r="T100">
-        <v>33.87553635074207</v>
+        <v>67.75107270148413</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.004136713851341452</v>
+        <v>0.004094928862944064</v>
       </c>
       <c r="W100">
-        <v>0.2348245628738537</v>
+        <v>0.2348344157741178</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.02068356925670722</v>
+        <v>0.02047464431472035</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2677027186548133</v>
-      </c>
-      <c r="C101">
-        <v>-3591.784804045802</v>
-      </c>
-      <c r="D101">
-        <v>677.8931959541978</v>
-      </c>
-      <c r="E101">
-        <v>4584.078</v>
-      </c>
-      <c r="F101">
-        <v>4744.277999999999</v>
-      </c>
-      <c r="G101">
-        <v>474.6</v>
-      </c>
-      <c r="H101">
-        <v>4632</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>30.875</v>
-      </c>
-      <c r="K101">
-        <v>7.97</v>
-      </c>
-      <c r="L101">
-        <v>22.905</v>
-      </c>
-      <c r="M101">
-        <v>1118.7007524</v>
-      </c>
-      <c r="N101">
-        <v>-1095.7957524</v>
-      </c>
-      <c r="O101">
-        <v>-219.15915048</v>
-      </c>
-      <c r="P101">
-        <v>-876.6366019199999</v>
-      </c>
-      <c r="Q101">
-        <v>-868.6666019199998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.521664703843666</v>
-      </c>
-      <c r="T101">
-        <v>67.75107270148413</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.004094928862944064</v>
-      </c>
-      <c r="W101">
-        <v>0.2348344157741178</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.02047464431472035</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
